--- a/research/traditional_assets/database/data/new_zealand/new_zealand_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_retail_grocery_and_food.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06924579469179407</v>
+        <v>0.06908430646665704</v>
       </c>
       <c r="C2">
-        <v>40.12895265672751</v>
+        <v>39.77157816085239</v>
       </c>
       <c r="D2">
-        <v>39.00895265672751</v>
+        <v>39.06457816085238</v>
       </c>
       <c r="E2">
-        <v>-12.7</v>
+        <v>-12.287</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="G2">
         <v>1.12</v>
@@ -1439,28 +1439,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0207739</v>
       </c>
       <c r="N2">
-        <v>7.083469387755102</v>
+        <v>7.062695487755102</v>
       </c>
       <c r="O2">
-        <v>1.983371428571429</v>
+        <v>1.977554736571429</v>
       </c>
       <c r="P2">
-        <v>5.100097959183673</v>
+        <v>5.085140751183673</v>
       </c>
       <c r="Q2">
-        <v>6.190097959183673</v>
+        <v>6.175140751183672</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06924579469179407</v>
+        <v>0.06941630956227984</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5454113062882181</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>340.9792762916497</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06908430646665704</v>
+        <v>0.06892281824152002</v>
       </c>
       <c r="C3">
-        <v>39.77157816085239</v>
+        <v>39.41436253185387</v>
       </c>
       <c r="D3">
-        <v>39.06457816085238</v>
+        <v>39.12036253185387</v>
       </c>
       <c r="E3">
-        <v>-12.287</v>
+        <v>-11.874</v>
       </c>
       <c r="F3">
-        <v>0.413</v>
+        <v>0.826</v>
       </c>
       <c r="G3">
         <v>1.12</v>
@@ -1521,28 +1521,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M3">
-        <v>0.0207739</v>
+        <v>0.0415478</v>
       </c>
       <c r="N3">
-        <v>7.062695487755102</v>
+        <v>7.041921587755102</v>
       </c>
       <c r="O3">
-        <v>1.977554736571429</v>
+        <v>1.971738044571429</v>
       </c>
       <c r="P3">
-        <v>5.085140751183673</v>
+        <v>5.070183543183673</v>
       </c>
       <c r="Q3">
-        <v>6.175140751183672</v>
+        <v>6.160183543183673</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06941630956227984</v>
+        <v>0.06959030432808165</v>
       </c>
       <c r="T3">
-        <v>0.5454113062882181</v>
+        <v>0.5494296611566202</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>340.9792762916497</v>
+        <v>170.4896381458249</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06892281824152002</v>
+        <v>0.06876133001638299</v>
       </c>
       <c r="C4">
-        <v>39.41436253185387</v>
+        <v>39.05730645129282</v>
       </c>
       <c r="D4">
-        <v>39.12036253185387</v>
+        <v>39.17630645129282</v>
       </c>
       <c r="E4">
-        <v>-11.874</v>
+        <v>-11.461</v>
       </c>
       <c r="F4">
-        <v>0.826</v>
+        <v>1.239</v>
       </c>
       <c r="G4">
         <v>1.12</v>
@@ -1603,28 +1603,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M4">
-        <v>0.0415478</v>
+        <v>0.06232169999999999</v>
       </c>
       <c r="N4">
-        <v>7.041921587755102</v>
+        <v>7.021147687755102</v>
       </c>
       <c r="O4">
-        <v>1.971738044571429</v>
+        <v>1.965921352571429</v>
       </c>
       <c r="P4">
-        <v>5.070183543183673</v>
+        <v>5.055226335183673</v>
       </c>
       <c r="Q4">
-        <v>6.160183543183673</v>
+        <v>6.145226335183673</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06959030432808165</v>
+        <v>0.06976788661482783</v>
       </c>
       <c r="T4">
-        <v>0.5494296611566202</v>
+        <v>0.5535308687027214</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>170.4896381458249</v>
+        <v>113.6597587638832</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06876133001638299</v>
+        <v>0.06859984179124597</v>
       </c>
       <c r="C5">
-        <v>39.05730645129282</v>
+        <v>38.70041060463428</v>
       </c>
       <c r="D5">
-        <v>39.17630645129282</v>
+        <v>39.23241060463428</v>
       </c>
       <c r="E5">
-        <v>-11.461</v>
+        <v>-11.048</v>
       </c>
       <c r="F5">
-        <v>1.239</v>
+        <v>1.652</v>
       </c>
       <c r="G5">
         <v>1.12</v>
@@ -1685,28 +1685,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M5">
-        <v>0.06232169999999999</v>
+        <v>0.08309559999999999</v>
       </c>
       <c r="N5">
-        <v>7.021147687755102</v>
+        <v>7.000373787755102</v>
       </c>
       <c r="O5">
-        <v>1.965921352571429</v>
+        <v>1.960104660571429</v>
       </c>
       <c r="P5">
-        <v>5.055226335183673</v>
+        <v>5.040269127183673</v>
       </c>
       <c r="Q5">
-        <v>6.145226335183673</v>
+        <v>6.130269127183673</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06976788661482783</v>
+        <v>0.06994916853254789</v>
       </c>
       <c r="T5">
-        <v>0.5535308687027214</v>
+        <v>0.5577175180726995</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>113.6597587638832</v>
+        <v>85.24481907291243</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06859984179124597</v>
+        <v>0.06843835356610896</v>
       </c>
       <c r="C6">
-        <v>38.70041060463428</v>
+        <v>38.34367568127559</v>
       </c>
       <c r="D6">
-        <v>39.23241060463428</v>
+        <v>39.28867568127559</v>
       </c>
       <c r="E6">
-        <v>-11.048</v>
+        <v>-10.635</v>
       </c>
       <c r="F6">
-        <v>1.652</v>
+        <v>2.065</v>
       </c>
       <c r="G6">
         <v>1.12</v>
@@ -1767,28 +1767,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M6">
-        <v>0.08309559999999999</v>
+        <v>0.1038695</v>
       </c>
       <c r="N6">
-        <v>7.000373787755102</v>
+        <v>6.979599887755102</v>
       </c>
       <c r="O6">
-        <v>1.960104660571429</v>
+        <v>1.954287968571429</v>
       </c>
       <c r="P6">
-        <v>5.040269127183673</v>
+        <v>5.025311919183673</v>
       </c>
       <c r="Q6">
-        <v>6.130269127183673</v>
+        <v>6.115311919183673</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06994916853254789</v>
+        <v>0.07013426691169364</v>
       </c>
       <c r="T6">
-        <v>0.5577175180726995</v>
+        <v>0.5619923074294142</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.24481907291243</v>
+        <v>68.19585525832994</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06843835356610896</v>
+        <v>0.06827686534097192</v>
       </c>
       <c r="C7">
-        <v>38.34367568127559</v>
+        <v>37.98710237457453</v>
       </c>
       <c r="D7">
-        <v>39.28867568127559</v>
+        <v>39.34510237457453</v>
       </c>
       <c r="E7">
-        <v>-10.635</v>
+        <v>-10.222</v>
       </c>
       <c r="F7">
-        <v>2.065</v>
+        <v>2.478</v>
       </c>
       <c r="G7">
         <v>1.12</v>
@@ -1849,28 +1849,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M7">
-        <v>0.1038695</v>
+        <v>0.1246434</v>
       </c>
       <c r="N7">
-        <v>6.979599887755102</v>
+        <v>6.958825987755102</v>
       </c>
       <c r="O7">
-        <v>1.954287968571429</v>
+        <v>1.948471276571429</v>
       </c>
       <c r="P7">
-        <v>5.025311919183673</v>
+        <v>5.010354711183673</v>
       </c>
       <c r="Q7">
-        <v>6.115311919183673</v>
+        <v>6.100354711183673</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07013426691169364</v>
+        <v>0.07032330355422545</v>
       </c>
       <c r="T7">
-        <v>0.5619923074294142</v>
+        <v>0.5663580497511653</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.19585525832994</v>
+        <v>56.82987938194162</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06827686534097192</v>
+        <v>0.0681153771158349</v>
       </c>
       <c r="C8">
-        <v>37.98710237457453</v>
+        <v>37.63069138187783</v>
       </c>
       <c r="D8">
-        <v>39.34510237457453</v>
+        <v>39.40169138187783</v>
       </c>
       <c r="E8">
-        <v>-10.222</v>
+        <v>-9.808999999999999</v>
       </c>
       <c r="F8">
-        <v>2.478</v>
+        <v>2.891</v>
       </c>
       <c r="G8">
         <v>1.12</v>
@@ -1931,28 +1931,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M8">
-        <v>0.1246434</v>
+        <v>0.1454173</v>
       </c>
       <c r="N8">
-        <v>6.958825987755102</v>
+        <v>6.938052087755102</v>
       </c>
       <c r="O8">
-        <v>1.948471276571429</v>
+        <v>1.942654584571429</v>
       </c>
       <c r="P8">
-        <v>5.010354711183673</v>
+        <v>4.995397503183673</v>
       </c>
       <c r="Q8">
-        <v>6.100354711183673</v>
+        <v>6.085397503183673</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07032330355422545</v>
+        <v>0.07051640550089774</v>
       </c>
       <c r="T8">
-        <v>0.5663580497511653</v>
+        <v>0.5708176790045669</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.82987938194162</v>
+        <v>48.71132518452139</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0681153771158349</v>
+        <v>0.06795388889069788</v>
       </c>
       <c r="C9">
-        <v>37.63069138187783</v>
+        <v>37.2744434045499</v>
       </c>
       <c r="D9">
-        <v>39.40169138187783</v>
+        <v>39.4584434045499</v>
       </c>
       <c r="E9">
-        <v>-9.808999999999999</v>
+        <v>-9.395999999999999</v>
       </c>
       <c r="F9">
-        <v>2.891</v>
+        <v>3.304</v>
       </c>
       <c r="G9">
         <v>1.12</v>
@@ -2013,28 +2013,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M9">
-        <v>0.1454173</v>
+        <v>0.1661912</v>
       </c>
       <c r="N9">
-        <v>6.938052087755102</v>
+        <v>6.917278187755102</v>
       </c>
       <c r="O9">
-        <v>1.942654584571429</v>
+        <v>1.936837892571429</v>
       </c>
       <c r="P9">
-        <v>4.995397503183673</v>
+        <v>4.980440295183673</v>
       </c>
       <c r="Q9">
-        <v>6.085397503183673</v>
+        <v>6.070440295183673</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07051640550089774</v>
+        <v>0.07071370531597596</v>
       </c>
       <c r="T9">
-        <v>0.5708176790045669</v>
+        <v>0.575374256719999</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.71132518452139</v>
+        <v>42.62240953645622</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06795388889069788</v>
+        <v>0.06779240066556087</v>
       </c>
       <c r="C10">
-        <v>37.2744434045499</v>
+        <v>36.91835914800181</v>
       </c>
       <c r="D10">
-        <v>39.4584434045499</v>
+        <v>39.51535914800181</v>
       </c>
       <c r="E10">
-        <v>-9.395999999999999</v>
+        <v>-8.983000000000001</v>
       </c>
       <c r="F10">
-        <v>3.304</v>
+        <v>3.717</v>
       </c>
       <c r="G10">
         <v>1.12</v>
@@ -2095,28 +2095,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M10">
-        <v>0.1661912</v>
+        <v>0.1869651</v>
       </c>
       <c r="N10">
-        <v>6.917278187755102</v>
+        <v>6.896504287755102</v>
       </c>
       <c r="O10">
-        <v>1.936837892571429</v>
+        <v>1.931021200571429</v>
       </c>
       <c r="P10">
-        <v>4.980440295183673</v>
+        <v>4.965483087183673</v>
       </c>
       <c r="Q10">
-        <v>6.070440295183673</v>
+        <v>6.055483087183672</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07071370531597596</v>
+        <v>0.07091534139072622</v>
       </c>
       <c r="T10">
-        <v>0.575374256719999</v>
+        <v>0.5800309790006055</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.62240953645622</v>
+        <v>37.88658625462775</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06779240066556087</v>
+        <v>0.06763091244042384</v>
       </c>
       <c r="C11">
-        <v>36.91835914800181</v>
+        <v>36.56243932172052</v>
       </c>
       <c r="D11">
-        <v>39.51535914800181</v>
+        <v>39.57243932172052</v>
       </c>
       <c r="E11">
-        <v>-8.983000000000001</v>
+        <v>-8.57</v>
       </c>
       <c r="F11">
-        <v>3.717</v>
+        <v>4.129999999999999</v>
       </c>
       <c r="G11">
         <v>1.12</v>
@@ -2177,28 +2177,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M11">
-        <v>0.1869651</v>
+        <v>0.207739</v>
       </c>
       <c r="N11">
-        <v>6.896504287755102</v>
+        <v>6.875730387755102</v>
       </c>
       <c r="O11">
-        <v>1.931021200571429</v>
+        <v>1.925204508571429</v>
       </c>
       <c r="P11">
-        <v>4.965483087183673</v>
+        <v>4.950525879183673</v>
       </c>
       <c r="Q11">
-        <v>6.055483087183672</v>
+        <v>6.040525879183673</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07091534139072622</v>
+        <v>0.07112145826713759</v>
       </c>
       <c r="T11">
-        <v>0.5800309790006055</v>
+        <v>0.5847911839985588</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.88658625462775</v>
+        <v>34.09792762916498</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06763091244042384</v>
+        <v>0.0674694242152868</v>
       </c>
       <c r="C12">
-        <v>36.56243932172052</v>
+        <v>36.20668463929835</v>
       </c>
       <c r="D12">
-        <v>39.57243932172052</v>
+        <v>39.62968463929835</v>
       </c>
       <c r="E12">
-        <v>-8.57</v>
+        <v>-8.157</v>
       </c>
       <c r="F12">
-        <v>4.13</v>
+        <v>4.543</v>
       </c>
       <c r="G12">
         <v>1.12</v>
@@ -2259,28 +2259,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M12">
-        <v>0.207739</v>
+        <v>0.2285129</v>
       </c>
       <c r="N12">
-        <v>6.875730387755102</v>
+        <v>6.854956487755102</v>
       </c>
       <c r="O12">
-        <v>1.925204508571429</v>
+        <v>1.919387816571429</v>
       </c>
       <c r="P12">
-        <v>4.950525879183673</v>
+        <v>4.935568671183673</v>
       </c>
       <c r="Q12">
-        <v>6.040525879183673</v>
+        <v>6.025568671183673</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07112145826713759</v>
+        <v>0.07133220698346832</v>
       </c>
       <c r="T12">
-        <v>0.5847911839985588</v>
+        <v>0.5896583598953424</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.09792762916497</v>
+        <v>30.99811602651361</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0674694242152868</v>
+        <v>0.06730793599014979</v>
       </c>
       <c r="C13">
-        <v>36.20668463929835</v>
+        <v>35.85109581846267</v>
       </c>
       <c r="D13">
-        <v>39.62968463929835</v>
+        <v>39.68709581846267</v>
       </c>
       <c r="E13">
-        <v>-8.157</v>
+        <v>-7.744</v>
       </c>
       <c r="F13">
-        <v>4.543</v>
+        <v>4.956</v>
       </c>
       <c r="G13">
         <v>1.12</v>
@@ -2341,28 +2341,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M13">
-        <v>0.2285129</v>
+        <v>0.2492868</v>
       </c>
       <c r="N13">
-        <v>6.854956487755102</v>
+        <v>6.834182587755102</v>
       </c>
       <c r="O13">
-        <v>1.919387816571429</v>
+        <v>1.913571124571429</v>
       </c>
       <c r="P13">
-        <v>4.935568671183673</v>
+        <v>4.920611463183673</v>
       </c>
       <c r="Q13">
-        <v>6.025568671183673</v>
+        <v>6.010611463183673</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07133220698346832</v>
+        <v>0.07154774544335203</v>
       </c>
       <c r="T13">
-        <v>0.5896583598953424</v>
+        <v>0.594636153426144</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.99811602651361</v>
+        <v>28.41493969097081</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06730793599014979</v>
+        <v>0.06714644776501276</v>
       </c>
       <c r="C14">
-        <v>35.85109581846267</v>
+        <v>35.49567358110604</v>
       </c>
       <c r="D14">
-        <v>39.68709581846267</v>
+        <v>39.74467358110604</v>
       </c>
       <c r="E14">
-        <v>-7.744</v>
+        <v>-7.331</v>
       </c>
       <c r="F14">
-        <v>4.956</v>
+        <v>5.369</v>
       </c>
       <c r="G14">
         <v>1.12</v>
@@ -2423,28 +2423,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M14">
-        <v>0.2492868</v>
+        <v>0.2700607</v>
       </c>
       <c r="N14">
-        <v>6.834182587755102</v>
+        <v>6.813408687755102</v>
       </c>
       <c r="O14">
-        <v>1.913571124571429</v>
+        <v>1.907754432571429</v>
       </c>
       <c r="P14">
-        <v>4.920611463183673</v>
+        <v>4.905654255183673</v>
       </c>
       <c r="Q14">
-        <v>6.010611463183673</v>
+        <v>5.995654255183673</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07154774544335203</v>
+        <v>0.0717682388103595</v>
       </c>
       <c r="T14">
-        <v>0.594636153426144</v>
+        <v>0.5997283789921363</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.41493969097081</v>
+        <v>26.22917509935767</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06714644776501276</v>
+        <v>0.06698495953987574</v>
       </c>
       <c r="C15">
-        <v>35.49567358110604</v>
+        <v>35.1404186533163</v>
       </c>
       <c r="D15">
-        <v>39.74467358110604</v>
+        <v>39.8024186533163</v>
       </c>
       <c r="E15">
-        <v>-7.331</v>
+        <v>-6.917999999999999</v>
       </c>
       <c r="F15">
-        <v>5.369</v>
+        <v>5.782</v>
       </c>
       <c r="G15">
         <v>1.12</v>
@@ -2505,28 +2505,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M15">
-        <v>0.2700607</v>
+        <v>0.2908346</v>
       </c>
       <c r="N15">
-        <v>6.813408687755102</v>
+        <v>6.792634787755102</v>
       </c>
       <c r="O15">
-        <v>1.907754432571429</v>
+        <v>1.901937740571429</v>
       </c>
       <c r="P15">
-        <v>4.905654255183673</v>
+        <v>4.890697047183673</v>
       </c>
       <c r="Q15">
-        <v>5.995654255183673</v>
+        <v>5.980697047183673</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0717682388103595</v>
+        <v>0.07199385993008807</v>
       </c>
       <c r="T15">
-        <v>0.5997283789921363</v>
+        <v>0.6049390284085004</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.22917509935767</v>
+        <v>24.35566259226069</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06698495953987574</v>
+        <v>0.06682347131473872</v>
       </c>
       <c r="C16">
-        <v>35.1404186533163</v>
+        <v>34.78533176540718</v>
       </c>
       <c r="D16">
-        <v>39.8024186533163</v>
+        <v>39.86033176540718</v>
       </c>
       <c r="E16">
-        <v>-6.917999999999999</v>
+        <v>-6.504999999999999</v>
       </c>
       <c r="F16">
-        <v>5.782</v>
+        <v>6.195</v>
       </c>
       <c r="G16">
         <v>1.12</v>
@@ -2587,28 +2587,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M16">
-        <v>0.2908346</v>
+        <v>0.3116085</v>
       </c>
       <c r="N16">
-        <v>6.792634787755102</v>
+        <v>6.771860887755102</v>
       </c>
       <c r="O16">
-        <v>1.901937740571429</v>
+        <v>1.896121048571429</v>
       </c>
       <c r="P16">
-        <v>4.890697047183673</v>
+        <v>4.875739839183673</v>
       </c>
       <c r="Q16">
-        <v>5.980697047183673</v>
+        <v>5.965739839183673</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07199385993008807</v>
+        <v>0.07222478978204555</v>
       </c>
       <c r="T16">
-        <v>0.6049390284085004</v>
+        <v>0.6102722813405439</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.35566259226069</v>
+        <v>22.73195175277665</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06682347131473872</v>
+        <v>0.0666619830896017</v>
       </c>
       <c r="C17">
-        <v>34.78533176540718</v>
+        <v>34.4304136519491</v>
       </c>
       <c r="D17">
-        <v>39.86033176540718</v>
+        <v>39.91841365194909</v>
       </c>
       <c r="E17">
-        <v>-6.505</v>
+        <v>-6.092</v>
       </c>
       <c r="F17">
-        <v>6.194999999999999</v>
+        <v>6.608</v>
       </c>
       <c r="G17">
         <v>1.12</v>
@@ -2669,28 +2669,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M17">
-        <v>0.3116085</v>
+        <v>0.3323824</v>
       </c>
       <c r="N17">
-        <v>6.771860887755102</v>
+        <v>6.751086987755102</v>
       </c>
       <c r="O17">
-        <v>1.896121048571429</v>
+        <v>1.890304356571429</v>
       </c>
       <c r="P17">
-        <v>4.875739839183673</v>
+        <v>4.860782631183673</v>
       </c>
       <c r="Q17">
-        <v>5.965739839183673</v>
+        <v>5.950782631183673</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07222478978204555</v>
+        <v>0.07246121796381154</v>
       </c>
       <c r="T17">
-        <v>0.6102722813405439</v>
+        <v>0.6157325164852551</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.73195175277665</v>
+        <v>21.31120476822811</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0666619830896017</v>
+        <v>0.06650049486446466</v>
       </c>
       <c r="C18">
-        <v>34.4304136519491</v>
+        <v>34.07566505180016</v>
       </c>
       <c r="D18">
-        <v>39.91841365194909</v>
+        <v>39.97666505180016</v>
       </c>
       <c r="E18">
-        <v>-6.092</v>
+        <v>-5.678999999999999</v>
       </c>
       <c r="F18">
-        <v>6.608</v>
+        <v>7.021</v>
       </c>
       <c r="G18">
         <v>1.12</v>
@@ -2751,28 +2751,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M18">
-        <v>0.3323824</v>
+        <v>0.3531563</v>
       </c>
       <c r="N18">
-        <v>6.751086987755102</v>
+        <v>6.730313087755102</v>
       </c>
       <c r="O18">
-        <v>1.890304356571429</v>
+        <v>1.884487664571429</v>
       </c>
       <c r="P18">
-        <v>4.860782631183673</v>
+        <v>4.845825423183673</v>
       </c>
       <c r="Q18">
-        <v>5.950782631183673</v>
+        <v>5.935825423183672</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07246121796381154</v>
+        <v>0.07270334321019839</v>
       </c>
       <c r="T18">
-        <v>0.6157325164852551</v>
+        <v>0.621324323561164</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.31120476822811</v>
+        <v>20.0576044877441</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06650049486446466</v>
+        <v>0.06633900663932764</v>
       </c>
       <c r="C19">
-        <v>34.07566505180016</v>
+        <v>33.72108670813754</v>
       </c>
       <c r="D19">
-        <v>39.97666505180016</v>
+        <v>40.03508670813754</v>
       </c>
       <c r="E19">
-        <v>-5.678999999999999</v>
+        <v>-5.265999999999999</v>
       </c>
       <c r="F19">
-        <v>7.021</v>
+        <v>7.434</v>
       </c>
       <c r="G19">
         <v>1.12</v>
@@ -2833,28 +2833,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M19">
-        <v>0.3531563</v>
+        <v>0.3739302</v>
       </c>
       <c r="N19">
-        <v>6.730313087755102</v>
+        <v>6.709539187755102</v>
       </c>
       <c r="O19">
-        <v>1.884487664571429</v>
+        <v>1.878670972571429</v>
       </c>
       <c r="P19">
-        <v>4.845825423183673</v>
+        <v>4.830868215183673</v>
       </c>
       <c r="Q19">
-        <v>5.935825423183672</v>
+        <v>5.920868215183673</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07270334321019839</v>
+        <v>0.07295137395039956</v>
       </c>
       <c r="T19">
-        <v>0.621324323561164</v>
+        <v>0.6270525161755097</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.0576044877441</v>
+        <v>18.94329312731387</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06633900663932765</v>
+        <v>0.06617751841419063</v>
       </c>
       <c r="C20">
-        <v>33.72108670813753</v>
+        <v>33.36667936848906</v>
       </c>
       <c r="D20">
-        <v>40.03508670813753</v>
+        <v>40.09367936848906</v>
       </c>
       <c r="E20">
-        <v>-5.266</v>
+        <v>-4.853</v>
       </c>
       <c r="F20">
-        <v>7.433999999999999</v>
+        <v>7.847</v>
       </c>
       <c r="G20">
         <v>1.12</v>
@@ -2915,28 +2915,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M20">
-        <v>0.3739301999999999</v>
+        <v>0.3947040999999999</v>
       </c>
       <c r="N20">
-        <v>6.709539187755102</v>
+        <v>6.688765287755102</v>
       </c>
       <c r="O20">
-        <v>1.878670972571429</v>
+        <v>1.872854280571429</v>
       </c>
       <c r="P20">
-        <v>4.830868215183673</v>
+        <v>4.815911007183673</v>
       </c>
       <c r="Q20">
-        <v>5.920868215183673</v>
+        <v>5.905911007183673</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07295137395039956</v>
+        <v>0.07320552890640818</v>
       </c>
       <c r="T20">
-        <v>0.6270525161755097</v>
+        <v>0.6329221456445306</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.94329312731388</v>
+        <v>17.94627769956051</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06617751841419063</v>
+        <v>0.0660160301890536</v>
       </c>
       <c r="C21">
-        <v>33.36667936848906</v>
+        <v>33.01244378476512</v>
       </c>
       <c r="D21">
-        <v>40.09367936848906</v>
+        <v>40.15244378476512</v>
       </c>
       <c r="E21">
-        <v>-4.853</v>
+        <v>-4.44</v>
       </c>
       <c r="F21">
-        <v>7.847</v>
+        <v>8.26</v>
       </c>
       <c r="G21">
         <v>1.12</v>
@@ -2997,28 +2997,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M21">
-        <v>0.3947040999999999</v>
+        <v>0.415478</v>
       </c>
       <c r="N21">
-        <v>6.688765287755102</v>
+        <v>6.667991387755102</v>
       </c>
       <c r="O21">
-        <v>1.872854280571429</v>
+        <v>1.867037588571429</v>
       </c>
       <c r="P21">
-        <v>4.815911007183673</v>
+        <v>4.800953799183673</v>
       </c>
       <c r="Q21">
-        <v>5.905911007183673</v>
+        <v>5.890953799183673</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07320552890640818</v>
+        <v>0.07346603773631699</v>
       </c>
       <c r="T21">
-        <v>0.6329221456445306</v>
+        <v>0.6389385158502772</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.94627769956051</v>
+        <v>17.04896381458249</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0660160301890536</v>
+        <v>0.06585454196391657</v>
       </c>
       <c r="C22">
-        <v>33.01244378476512</v>
+        <v>32.65838071329075</v>
       </c>
       <c r="D22">
-        <v>40.15244378476512</v>
+        <v>40.21138071329075</v>
       </c>
       <c r="E22">
-        <v>-4.44</v>
+        <v>-4.026999999999999</v>
       </c>
       <c r="F22">
-        <v>8.26</v>
+        <v>8.673</v>
       </c>
       <c r="G22">
         <v>1.12</v>
@@ -3079,28 +3079,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M22">
-        <v>0.415478</v>
+        <v>0.4362519</v>
       </c>
       <c r="N22">
-        <v>6.667991387755102</v>
+        <v>6.647217487755102</v>
       </c>
       <c r="O22">
-        <v>1.867037588571429</v>
+        <v>1.861220896571429</v>
       </c>
       <c r="P22">
-        <v>4.800953799183673</v>
+        <v>4.785996591183673</v>
       </c>
       <c r="Q22">
-        <v>5.890953799183673</v>
+        <v>5.875996591183673</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07346603773631699</v>
+        <v>0.07373314172647667</v>
       </c>
       <c r="T22">
-        <v>0.6389385158502772</v>
+        <v>0.6451071992257894</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.04896381458249</v>
+        <v>16.23710839484046</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06585454196391657</v>
+        <v>0.06569305373877955</v>
       </c>
       <c r="C23">
-        <v>32.65838071329075</v>
+        <v>32.3044909148382</v>
       </c>
       <c r="D23">
-        <v>40.21138071329075</v>
+        <v>40.27049091483821</v>
       </c>
       <c r="E23">
-        <v>-4.027000000000001</v>
+        <v>-3.613999999999999</v>
       </c>
       <c r="F23">
-        <v>8.672999999999998</v>
+        <v>9.086</v>
       </c>
       <c r="G23">
         <v>1.12</v>
@@ -3161,28 +3161,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M23">
-        <v>0.4362518999999999</v>
+        <v>0.4570258</v>
       </c>
       <c r="N23">
-        <v>6.647217487755102</v>
+        <v>6.626443587755102</v>
       </c>
       <c r="O23">
-        <v>1.861220896571429</v>
+        <v>1.855404204571429</v>
       </c>
       <c r="P23">
-        <v>4.785996591183673</v>
+        <v>4.771039383183673</v>
       </c>
       <c r="Q23">
-        <v>5.875996591183673</v>
+        <v>5.861039383183673</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07373314172647667</v>
+        <v>0.07400709453689686</v>
       </c>
       <c r="T23">
-        <v>0.6451071992257894</v>
+        <v>0.6514340539699045</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.23710839484047</v>
+        <v>15.49905801325681</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06569305373877955</v>
+        <v>0.06553156551364253</v>
       </c>
       <c r="C24">
-        <v>32.3044909148382</v>
+        <v>31.95077515465957</v>
       </c>
       <c r="D24">
-        <v>40.27049091483821</v>
+        <v>40.32977515465958</v>
       </c>
       <c r="E24">
-        <v>-3.613999999999999</v>
+        <v>-3.200999999999999</v>
       </c>
       <c r="F24">
-        <v>9.086</v>
+        <v>9.499000000000001</v>
       </c>
       <c r="G24">
         <v>1.12</v>
@@ -3243,28 +3243,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M24">
-        <v>0.4570258</v>
+        <v>0.4777997</v>
       </c>
       <c r="N24">
-        <v>6.626443587755102</v>
+        <v>6.605669687755102</v>
       </c>
       <c r="O24">
-        <v>1.855404204571429</v>
+        <v>1.849587512571429</v>
       </c>
       <c r="P24">
-        <v>4.771039383183673</v>
+        <v>4.756082175183673</v>
       </c>
       <c r="Q24">
-        <v>5.861039383183673</v>
+        <v>5.846082175183673</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07400709453689686</v>
+        <v>0.07428816300473055</v>
       </c>
       <c r="T24">
-        <v>0.6514340539699045</v>
+        <v>0.6579252426034771</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.49905801325681</v>
+        <v>14.8251859257239</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06553156551364253</v>
+        <v>0.06537007728850551</v>
       </c>
       <c r="C25">
-        <v>31.95077515465957</v>
+        <v>31.59723420251989</v>
       </c>
       <c r="D25">
-        <v>40.32977515465958</v>
+        <v>40.38923420251989</v>
       </c>
       <c r="E25">
-        <v>-3.200999999999999</v>
+        <v>-2.787999999999998</v>
       </c>
       <c r="F25">
-        <v>9.499000000000001</v>
+        <v>9.912000000000001</v>
       </c>
       <c r="G25">
         <v>1.12</v>
@@ -3325,28 +3325,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M25">
-        <v>0.4777997</v>
+        <v>0.4985736</v>
       </c>
       <c r="N25">
-        <v>6.605669687755102</v>
+        <v>6.584895787755102</v>
       </c>
       <c r="O25">
-        <v>1.849587512571429</v>
+        <v>1.843770820571429</v>
       </c>
       <c r="P25">
-        <v>4.756082175183673</v>
+        <v>4.741124967183673</v>
       </c>
       <c r="Q25">
-        <v>5.846082175183673</v>
+        <v>5.831124967183673</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07428816300473055</v>
+        <v>0.07457662801119146</v>
       </c>
       <c r="T25">
-        <v>0.6579252426034771</v>
+        <v>0.6645872519905649</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.8251859257239</v>
+        <v>14.2074698454854</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06537007728850551</v>
+        <v>0.06520858906336847</v>
       </c>
       <c r="C26">
-        <v>31.59723420251989</v>
+        <v>31.2438688327304</v>
       </c>
       <c r="D26">
-        <v>40.38923420251989</v>
+        <v>40.4488688327304</v>
       </c>
       <c r="E26">
-        <v>-2.788</v>
+        <v>-2.375</v>
       </c>
       <c r="F26">
-        <v>9.911999999999999</v>
+        <v>10.325</v>
       </c>
       <c r="G26">
         <v>1.12</v>
@@ -3407,28 +3407,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M26">
-        <v>0.4985736</v>
+        <v>0.5193475</v>
       </c>
       <c r="N26">
-        <v>6.584895787755102</v>
+        <v>6.564121887755102</v>
       </c>
       <c r="O26">
-        <v>1.843770820571429</v>
+        <v>1.837954128571429</v>
       </c>
       <c r="P26">
-        <v>4.741124967183673</v>
+        <v>4.726167759183673</v>
       </c>
       <c r="Q26">
-        <v>5.831124967183673</v>
+        <v>5.816167759183672</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07457662801119146</v>
+        <v>0.07487278541782463</v>
       </c>
       <c r="T26">
-        <v>0.6645872519905649</v>
+        <v>0.6714269149613082</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.20746984548541</v>
+        <v>13.63917105166599</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06520858906336847</v>
+        <v>0.06504710083823145</v>
       </c>
       <c r="C27">
-        <v>31.2438688327304</v>
+        <v>30.89067982418219</v>
       </c>
       <c r="D27">
-        <v>40.4488688327304</v>
+        <v>40.50867982418219</v>
       </c>
       <c r="E27">
-        <v>-2.375</v>
+        <v>-1.962</v>
       </c>
       <c r="F27">
-        <v>10.325</v>
+        <v>10.738</v>
       </c>
       <c r="G27">
         <v>1.12</v>
@@ -3489,28 +3489,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M27">
-        <v>0.5193475</v>
+        <v>0.5401214</v>
       </c>
       <c r="N27">
-        <v>6.564121887755102</v>
+        <v>6.543347987755102</v>
       </c>
       <c r="O27">
-        <v>1.837954128571429</v>
+        <v>1.832137436571429</v>
       </c>
       <c r="P27">
-        <v>4.726167759183673</v>
+        <v>4.711210551183672</v>
       </c>
       <c r="Q27">
-        <v>5.816167759183672</v>
+        <v>5.801210551183672</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07487278541782463</v>
+        <v>0.07517694707869116</v>
       </c>
       <c r="T27">
-        <v>0.6714269149613082</v>
+        <v>0.6784514336880176</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.63917105166599</v>
+        <v>13.11458754967883</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06504710083823145</v>
+        <v>0.06517721261309443</v>
       </c>
       <c r="C28">
-        <v>30.89067982418219</v>
+        <v>30.42947601614359</v>
       </c>
       <c r="D28">
-        <v>40.50867982418219</v>
+        <v>40.46047601614359</v>
       </c>
       <c r="E28">
-        <v>-1.962</v>
+        <v>-1.548999999999999</v>
       </c>
       <c r="F28">
-        <v>10.738</v>
+        <v>11.151</v>
       </c>
       <c r="G28">
         <v>1.12</v>
@@ -3571,45 +3571,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M28">
-        <v>0.5401214</v>
+        <v>0.5776218</v>
       </c>
       <c r="N28">
-        <v>6.543347987755102</v>
+        <v>6.505847587755102</v>
       </c>
       <c r="O28">
-        <v>1.832137436571429</v>
+        <v>1.821637324571429</v>
       </c>
       <c r="P28">
-        <v>4.711210551183672</v>
+        <v>4.684210263183673</v>
       </c>
       <c r="Q28">
-        <v>5.801210551183672</v>
+        <v>5.774210263183673</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07517694707869116</v>
+        <v>0.0754894419357458</v>
       </c>
       <c r="T28">
-        <v>0.6784514336880176</v>
+        <v>0.6856684049825821</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.28</v>
       </c>
       <c r="W28">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.11458754967883</v>
+        <v>12.26316144535248</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06517721261309443</v>
+        <v>0.0650265243879574</v>
       </c>
       <c r="C29">
-        <v>30.42947601614359</v>
+        <v>30.07231350746213</v>
       </c>
       <c r="D29">
-        <v>40.46047601614359</v>
+        <v>40.51631350746213</v>
       </c>
       <c r="E29">
-        <v>-1.548999999999999</v>
+        <v>-1.135999999999999</v>
       </c>
       <c r="F29">
-        <v>11.151</v>
+        <v>11.564</v>
       </c>
       <c r="G29">
         <v>1.12</v>
@@ -3653,28 +3653,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M29">
-        <v>0.5776218</v>
+        <v>0.5990152</v>
       </c>
       <c r="N29">
-        <v>6.505847587755102</v>
+        <v>6.484454187755102</v>
       </c>
       <c r="O29">
-        <v>1.821637324571429</v>
+        <v>1.815647172571429</v>
       </c>
       <c r="P29">
-        <v>4.684210263183673</v>
+        <v>4.668807015183673</v>
       </c>
       <c r="Q29">
-        <v>5.774210263183673</v>
+        <v>5.758807015183673</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0754894419357458</v>
+        <v>0.07581061720549639</v>
       </c>
       <c r="T29">
-        <v>0.6856684049825821</v>
+        <v>0.6930858477019955</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.26316144535248</v>
+        <v>11.82519139373275</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0650265243879574</v>
+        <v>0.06487583616282039</v>
       </c>
       <c r="C30">
-        <v>30.07231350746213</v>
+        <v>29.71530532885516</v>
       </c>
       <c r="D30">
-        <v>40.51631350746213</v>
+        <v>40.57230532885516</v>
       </c>
       <c r="E30">
-        <v>-1.135999999999999</v>
+        <v>-0.722999999999999</v>
       </c>
       <c r="F30">
-        <v>11.564</v>
+        <v>11.977</v>
       </c>
       <c r="G30">
         <v>1.12</v>
@@ -3735,28 +3735,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M30">
-        <v>0.5990152</v>
+        <v>0.6204086</v>
       </c>
       <c r="N30">
-        <v>6.484454187755102</v>
+        <v>6.463060787755102</v>
       </c>
       <c r="O30">
-        <v>1.815647172571429</v>
+        <v>1.809657020571429</v>
       </c>
       <c r="P30">
-        <v>4.668807015183673</v>
+        <v>4.653403767183673</v>
       </c>
       <c r="Q30">
-        <v>5.758807015183673</v>
+        <v>5.743403767183673</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07581061720549639</v>
+        <v>0.0761408396659442</v>
       </c>
       <c r="T30">
-        <v>0.6930858477019955</v>
+        <v>0.7007122324698433</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.82519139373275</v>
+        <v>11.41742617325921</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06487583616282037</v>
+        <v>0.06472514793768336</v>
       </c>
       <c r="C31">
-        <v>29.71530532885516</v>
+        <v>29.35845212104091</v>
       </c>
       <c r="D31">
-        <v>40.57230532885516</v>
+        <v>40.62845212104092</v>
       </c>
       <c r="E31">
-        <v>-0.7230000000000008</v>
+        <v>-0.3100000000000005</v>
       </c>
       <c r="F31">
-        <v>11.977</v>
+        <v>12.39</v>
       </c>
       <c r="G31">
         <v>1.12</v>
@@ -3817,28 +3817,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M31">
-        <v>0.6204085999999999</v>
+        <v>0.6418019999999999</v>
       </c>
       <c r="N31">
-        <v>6.463060787755102</v>
+        <v>6.441667387755102</v>
       </c>
       <c r="O31">
-        <v>1.809657020571429</v>
+        <v>1.803666868571429</v>
       </c>
       <c r="P31">
-        <v>4.653403767183673</v>
+        <v>4.638000519183673</v>
       </c>
       <c r="Q31">
-        <v>5.743403767183673</v>
+        <v>5.728000519183673</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0761408396659442</v>
+        <v>0.07648049705383338</v>
       </c>
       <c r="T31">
-        <v>0.7007122324698433</v>
+        <v>0.7085565139453438</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.41742617325921</v>
+        <v>11.03684530081724</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06472514793768336</v>
+        <v>0.06457445971254634</v>
       </c>
       <c r="C32">
-        <v>29.35845212104091</v>
+        <v>29.00175452828923</v>
       </c>
       <c r="D32">
-        <v>40.62845212104092</v>
+        <v>40.68475452828923</v>
       </c>
       <c r="E32">
-        <v>-0.3100000000000005</v>
+        <v>0.1029999999999998</v>
       </c>
       <c r="F32">
-        <v>12.39</v>
+        <v>12.803</v>
       </c>
       <c r="G32">
         <v>1.12</v>
@@ -3899,28 +3899,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M32">
-        <v>0.6418019999999999</v>
+        <v>0.6631954</v>
       </c>
       <c r="N32">
-        <v>6.441667387755102</v>
+        <v>6.420273987755102</v>
       </c>
       <c r="O32">
-        <v>1.803666868571429</v>
+        <v>1.797676716571429</v>
       </c>
       <c r="P32">
-        <v>4.638000519183673</v>
+        <v>4.622597271183673</v>
       </c>
       <c r="Q32">
-        <v>5.728000519183673</v>
+        <v>5.712597271183673</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07648049705383338</v>
+        <v>0.07682999958340049</v>
       </c>
       <c r="T32">
-        <v>0.7085565139453438</v>
+        <v>0.7166281658983948</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.03684530081724</v>
+        <v>10.68081803304893</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06457445971254634</v>
+        <v>0.06442377148740931</v>
       </c>
       <c r="C33">
-        <v>29.00175452828923</v>
+        <v>28.64521319844619</v>
       </c>
       <c r="D33">
-        <v>40.68475452828923</v>
+        <v>40.7412131984462</v>
       </c>
       <c r="E33">
-        <v>0.1029999999999998</v>
+        <v>0.516</v>
       </c>
       <c r="F33">
-        <v>12.803</v>
+        <v>13.216</v>
       </c>
       <c r="G33">
         <v>1.12</v>
@@ -3981,28 +3981,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M33">
-        <v>0.6631954</v>
+        <v>0.6845888</v>
       </c>
       <c r="N33">
-        <v>6.420273987755102</v>
+        <v>6.398880587755102</v>
       </c>
       <c r="O33">
-        <v>1.797676716571429</v>
+        <v>1.791686564571429</v>
       </c>
       <c r="P33">
-        <v>4.622597271183673</v>
+        <v>4.607194023183673</v>
       </c>
       <c r="Q33">
-        <v>5.712597271183673</v>
+        <v>5.697194023183673</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07682999958340049</v>
+        <v>0.07718978159913134</v>
       </c>
       <c r="T33">
-        <v>0.7166281658983948</v>
+        <v>0.724937219379477</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.68081803304893</v>
+        <v>10.34704246951616</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06442377148740931</v>
+        <v>0.06427308326227228</v>
       </c>
       <c r="C34">
-        <v>28.64521319844619</v>
+        <v>28.28882878295895</v>
       </c>
       <c r="D34">
-        <v>40.7412131984462</v>
+        <v>40.79782878295895</v>
       </c>
       <c r="E34">
-        <v>0.516</v>
+        <v>0.9290000000000003</v>
       </c>
       <c r="F34">
-        <v>13.216</v>
+        <v>13.629</v>
       </c>
       <c r="G34">
         <v>1.12</v>
@@ -4063,28 +4063,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M34">
-        <v>0.6845888</v>
+        <v>0.7059822</v>
       </c>
       <c r="N34">
-        <v>6.398880587755102</v>
+        <v>6.377487187755102</v>
       </c>
       <c r="O34">
-        <v>1.791686564571429</v>
+        <v>1.785696412571429</v>
       </c>
       <c r="P34">
-        <v>4.607194023183673</v>
+        <v>4.591790775183673</v>
       </c>
       <c r="Q34">
-        <v>5.697194023183673</v>
+        <v>5.681790775183673</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07718978159913134</v>
+        <v>0.07756030337652581</v>
       </c>
       <c r="T34">
-        <v>0.724937219379477</v>
+        <v>0.7334943043077556</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.34704246951616</v>
+        <v>10.03349572801567</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06427308326227228</v>
+        <v>0.06453855503713526</v>
       </c>
       <c r="C35">
-        <v>28.28882878295895</v>
+        <v>27.7761928025171</v>
       </c>
       <c r="D35">
-        <v>40.79782878295895</v>
+        <v>40.69819280251711</v>
       </c>
       <c r="E35">
-        <v>0.9290000000000003</v>
+        <v>1.342000000000001</v>
       </c>
       <c r="F35">
-        <v>13.629</v>
+        <v>14.042</v>
       </c>
       <c r="G35">
         <v>1.12</v>
@@ -4145,45 +4145,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M35">
-        <v>0.7059822</v>
+        <v>0.751247</v>
       </c>
       <c r="N35">
-        <v>6.377487187755102</v>
+        <v>6.332222387755102</v>
       </c>
       <c r="O35">
-        <v>1.785696412571429</v>
+        <v>1.773022268571429</v>
       </c>
       <c r="P35">
-        <v>4.591790775183673</v>
+        <v>4.559200119183673</v>
       </c>
       <c r="Q35">
-        <v>5.681790775183673</v>
+        <v>5.649200119183673</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07756030337652581</v>
+        <v>0.0779420530865686</v>
       </c>
       <c r="T35">
-        <v>0.7334943043077556</v>
+        <v>0.7423106948399215</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.28</v>
       </c>
       <c r="W35">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>10.03349572801567</v>
+        <v>9.428948651715217</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06453855503713526</v>
+        <v>0.06440010681199825</v>
       </c>
       <c r="C36">
-        <v>27.7761928025171</v>
+        <v>27.4150939310325</v>
       </c>
       <c r="D36">
-        <v>40.69819280251711</v>
+        <v>40.7500939310325</v>
       </c>
       <c r="E36">
-        <v>1.342000000000001</v>
+        <v>1.755000000000001</v>
       </c>
       <c r="F36">
-        <v>14.042</v>
+        <v>14.455</v>
       </c>
       <c r="G36">
         <v>1.12</v>
@@ -4227,28 +4227,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M36">
-        <v>0.751247</v>
+        <v>0.7733425</v>
       </c>
       <c r="N36">
-        <v>6.332222387755102</v>
+        <v>6.310126887755102</v>
       </c>
       <c r="O36">
-        <v>1.773022268571429</v>
+        <v>1.766835528571429</v>
       </c>
       <c r="P36">
-        <v>4.559200119183673</v>
+        <v>4.543291359183673</v>
       </c>
       <c r="Q36">
-        <v>5.649200119183673</v>
+        <v>5.633291359183673</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0779420530865686</v>
+        <v>0.07833554894153577</v>
       </c>
       <c r="T36">
-        <v>0.7423106948399215</v>
+        <v>0.7513983589269232</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.428948651715217</v>
+        <v>9.159550118809067</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06440010681199825</v>
+        <v>0.06426165858686121</v>
       </c>
       <c r="C37">
-        <v>27.4150939310325</v>
+        <v>27.05412760434008</v>
       </c>
       <c r="D37">
-        <v>40.7500939310325</v>
+        <v>40.80212760434009</v>
       </c>
       <c r="E37">
-        <v>1.755000000000001</v>
+        <v>2.168000000000001</v>
       </c>
       <c r="F37">
-        <v>14.455</v>
+        <v>14.868</v>
       </c>
       <c r="G37">
         <v>1.12</v>
@@ -4309,28 +4309,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M37">
-        <v>0.7733425</v>
+        <v>0.795438</v>
       </c>
       <c r="N37">
-        <v>6.310126887755102</v>
+        <v>6.288031387755102</v>
       </c>
       <c r="O37">
-        <v>1.766835528571429</v>
+        <v>1.760648788571429</v>
       </c>
       <c r="P37">
-        <v>4.543291359183673</v>
+        <v>4.527382599183673</v>
       </c>
       <c r="Q37">
-        <v>5.633291359183673</v>
+        <v>5.617382599183673</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07833554894153577</v>
+        <v>0.07874134154197066</v>
       </c>
       <c r="T37">
-        <v>0.7513983589269232</v>
+        <v>0.7607700125166436</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.159550118809067</v>
+        <v>8.905118171064373</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06426165858686123</v>
+        <v>0.06412321036172419</v>
       </c>
       <c r="C38">
-        <v>27.05412760434007</v>
+        <v>26.69329433082713</v>
       </c>
       <c r="D38">
-        <v>40.80212760434007</v>
+        <v>40.85429433082713</v>
       </c>
       <c r="E38">
-        <v>2.167999999999999</v>
+        <v>2.581</v>
       </c>
       <c r="F38">
-        <v>14.868</v>
+        <v>15.281</v>
       </c>
       <c r="G38">
         <v>1.12</v>
@@ -4391,28 +4391,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M38">
-        <v>0.7954379999999999</v>
+        <v>0.8175334999999999</v>
       </c>
       <c r="N38">
-        <v>6.288031387755102</v>
+        <v>6.265935887755102</v>
       </c>
       <c r="O38">
-        <v>1.760648788571429</v>
+        <v>1.754462048571429</v>
       </c>
       <c r="P38">
-        <v>4.527382599183673</v>
+        <v>4.511473839183673</v>
       </c>
       <c r="Q38">
-        <v>5.617382599183673</v>
+        <v>5.601473839183673</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07874134154197066</v>
+        <v>0.07916001644718126</v>
       </c>
       <c r="T38">
-        <v>0.7607700125166436</v>
+        <v>0.7704391789187361</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.905118171064373</v>
+        <v>8.664439301576147</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06412321036172419</v>
+        <v>0.06398476213658717</v>
       </c>
       <c r="C39">
-        <v>26.69329433082713</v>
+        <v>26.33259462148424</v>
       </c>
       <c r="D39">
-        <v>40.85429433082713</v>
+        <v>40.90659462148424</v>
       </c>
       <c r="E39">
-        <v>2.581</v>
+        <v>2.994</v>
       </c>
       <c r="F39">
-        <v>15.281</v>
+        <v>15.694</v>
       </c>
       <c r="G39">
         <v>1.12</v>
@@ -4473,28 +4473,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M39">
-        <v>0.8175334999999999</v>
+        <v>0.839629</v>
       </c>
       <c r="N39">
-        <v>6.265935887755102</v>
+        <v>6.243840387755101</v>
       </c>
       <c r="O39">
-        <v>1.754462048571429</v>
+        <v>1.748275308571429</v>
       </c>
       <c r="P39">
-        <v>4.511473839183673</v>
+        <v>4.495565079183673</v>
       </c>
       <c r="Q39">
-        <v>5.601473839183673</v>
+        <v>5.585565079183673</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07916001644718126</v>
+        <v>0.07959219699449545</v>
       </c>
       <c r="T39">
-        <v>0.7704391789187361</v>
+        <v>0.7804202539144447</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.664439301576147</v>
+        <v>8.436427741008352</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06398476213658717</v>
+        <v>0.06384631391145015</v>
       </c>
       <c r="C40">
-        <v>26.33259462148424</v>
+        <v>25.97202898992196</v>
       </c>
       <c r="D40">
-        <v>40.90659462148424</v>
+        <v>40.95902898992196</v>
       </c>
       <c r="E40">
-        <v>2.994</v>
+        <v>3.407</v>
       </c>
       <c r="F40">
-        <v>15.694</v>
+        <v>16.107</v>
       </c>
       <c r="G40">
         <v>1.12</v>
@@ -4555,28 +4555,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M40">
-        <v>0.839629</v>
+        <v>0.8617244999999999</v>
       </c>
       <c r="N40">
-        <v>6.243840387755101</v>
+        <v>6.221744887755102</v>
       </c>
       <c r="O40">
-        <v>1.748275308571429</v>
+        <v>1.742088568571429</v>
       </c>
       <c r="P40">
-        <v>4.495565079183673</v>
+        <v>4.479656319183673</v>
       </c>
       <c r="Q40">
-        <v>5.585565079183673</v>
+        <v>5.569656319183673</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07959219699449545</v>
+        <v>0.08003854739581992</v>
       </c>
       <c r="T40">
-        <v>0.7804202539144447</v>
+        <v>0.7907285772706681</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.436427741008352</v>
+        <v>8.220109080982498</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06384631391145015</v>
+        <v>0.06370786568631313</v>
       </c>
       <c r="C41">
-        <v>25.97202898992196</v>
+        <v>25.61159795238764</v>
       </c>
       <c r="D41">
-        <v>40.95902898992196</v>
+        <v>41.01159795238764</v>
       </c>
       <c r="E41">
-        <v>3.407</v>
+        <v>3.82</v>
       </c>
       <c r="F41">
-        <v>16.107</v>
+        <v>16.52</v>
       </c>
       <c r="G41">
         <v>1.12</v>
@@ -4637,28 +4637,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M41">
-        <v>0.8617244999999999</v>
+        <v>0.8838199999999999</v>
       </c>
       <c r="N41">
-        <v>6.221744887755102</v>
+        <v>6.199649387755102</v>
       </c>
       <c r="O41">
-        <v>1.742088568571429</v>
+        <v>1.735901828571429</v>
       </c>
       <c r="P41">
-        <v>4.479656319183673</v>
+        <v>4.463747559183673</v>
       </c>
       <c r="Q41">
-        <v>5.569656319183673</v>
+        <v>5.553747559183673</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08003854739581992</v>
+        <v>0.08049977614385521</v>
       </c>
       <c r="T41">
-        <v>0.7907285772706681</v>
+        <v>0.8013805114054324</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.220109080982498</v>
+        <v>8.014606353957936</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06370786568631313</v>
+        <v>0.0635694174611761</v>
       </c>
       <c r="C42">
-        <v>25.61159795238764</v>
+        <v>25.25130202778232</v>
       </c>
       <c r="D42">
-        <v>41.01159795238764</v>
+        <v>41.06430202778232</v>
       </c>
       <c r="E42">
-        <v>3.82</v>
+        <v>4.233000000000001</v>
       </c>
       <c r="F42">
-        <v>16.52</v>
+        <v>16.933</v>
       </c>
       <c r="G42">
         <v>1.12</v>
@@ -4719,28 +4719,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M42">
-        <v>0.8838199999999999</v>
+        <v>0.9059155</v>
       </c>
       <c r="N42">
-        <v>6.199649387755102</v>
+        <v>6.177553887755102</v>
       </c>
       <c r="O42">
-        <v>1.735901828571429</v>
+        <v>1.729715088571429</v>
       </c>
       <c r="P42">
-        <v>4.463747559183673</v>
+        <v>4.447838799183673</v>
       </c>
       <c r="Q42">
-        <v>5.553747559183673</v>
+        <v>5.537838799183673</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08049977614385521</v>
+        <v>0.08097663976470526</v>
       </c>
       <c r="T42">
-        <v>0.8013805114054324</v>
+        <v>0.8123935280532396</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.014606353957936</v>
+        <v>7.819128150202864</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0635694174611761</v>
+        <v>0.06343096923603908</v>
       </c>
       <c r="C43">
-        <v>25.25130202778232</v>
+        <v>24.89114173767785</v>
       </c>
       <c r="D43">
-        <v>41.06430202778232</v>
+        <v>41.11714173767785</v>
       </c>
       <c r="E43">
-        <v>4.233000000000001</v>
+        <v>4.646000000000001</v>
       </c>
       <c r="F43">
-        <v>16.933</v>
+        <v>17.346</v>
       </c>
       <c r="G43">
         <v>1.12</v>
@@ -4801,28 +4801,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M43">
-        <v>0.9059155</v>
+        <v>0.928011</v>
       </c>
       <c r="N43">
-        <v>6.177553887755102</v>
+        <v>6.155458387755102</v>
       </c>
       <c r="O43">
-        <v>1.729715088571429</v>
+        <v>1.723528348571429</v>
       </c>
       <c r="P43">
-        <v>4.447838799183673</v>
+        <v>4.431930039183674</v>
       </c>
       <c r="Q43">
-        <v>5.537838799183673</v>
+        <v>5.521930039183673</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08097663976470526</v>
+        <v>0.08146994695868807</v>
       </c>
       <c r="T43">
-        <v>0.8123935280532396</v>
+        <v>0.8237863038957987</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.819128150202864</v>
+        <v>7.632958432340891</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06343096923603909</v>
+        <v>0.06354020101090206</v>
       </c>
       <c r="C44">
-        <v>24.89114173767784</v>
+        <v>24.43644137658044</v>
       </c>
       <c r="D44">
-        <v>41.11714173767784</v>
+        <v>41.07544137658044</v>
       </c>
       <c r="E44">
-        <v>4.645999999999997</v>
+        <v>5.058999999999997</v>
       </c>
       <c r="F44">
-        <v>17.346</v>
+        <v>17.759</v>
       </c>
       <c r="G44">
         <v>1.12</v>
@@ -4883,45 +4883,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M44">
-        <v>0.9280109999999998</v>
+        <v>0.9643136999999998</v>
       </c>
       <c r="N44">
-        <v>6.155458387755102</v>
+        <v>6.119155687755102</v>
       </c>
       <c r="O44">
-        <v>1.723528348571429</v>
+        <v>1.713363592571429</v>
       </c>
       <c r="P44">
-        <v>4.431930039183674</v>
+        <v>4.405792095183673</v>
       </c>
       <c r="Q44">
-        <v>5.521930039183673</v>
+        <v>5.495792095183673</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08146994695868807</v>
+        <v>0.08198056317702115</v>
       </c>
       <c r="T44">
-        <v>0.8237863038957987</v>
+        <v>0.8355788262591493</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.28</v>
       </c>
       <c r="W44">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.632958432340891</v>
+        <v>7.345606919983718</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06354020101090206</v>
+        <v>0.06340751278576504</v>
       </c>
       <c r="C45">
-        <v>24.43644137658044</v>
+        <v>24.07410752603681</v>
       </c>
       <c r="D45">
-        <v>41.07544137658044</v>
+        <v>41.12610752603681</v>
       </c>
       <c r="E45">
-        <v>5.058999999999997</v>
+        <v>5.472000000000001</v>
       </c>
       <c r="F45">
-        <v>17.759</v>
+        <v>18.172</v>
       </c>
       <c r="G45">
         <v>1.12</v>
@@ -4965,28 +4965,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M45">
-        <v>0.9643136999999998</v>
+        <v>0.9867396</v>
       </c>
       <c r="N45">
-        <v>6.119155687755102</v>
+        <v>6.096729787755102</v>
       </c>
       <c r="O45">
-        <v>1.713363592571429</v>
+        <v>1.707084340571429</v>
       </c>
       <c r="P45">
-        <v>4.405792095183673</v>
+        <v>4.389645447183673</v>
       </c>
       <c r="Q45">
-        <v>5.495792095183673</v>
+        <v>5.479645447183673</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08198056317702115</v>
+        <v>0.08250941568886613</v>
       </c>
       <c r="T45">
-        <v>0.8355788262591493</v>
+        <v>0.8477925101354769</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.345606919983718</v>
+        <v>7.178661308165904</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06340751278576504</v>
+        <v>0.06327482456062801</v>
       </c>
       <c r="C46">
-        <v>24.07410752603681</v>
+        <v>23.71189882224591</v>
       </c>
       <c r="D46">
-        <v>41.12610752603681</v>
+        <v>41.17689882224592</v>
       </c>
       <c r="E46">
-        <v>5.472000000000001</v>
+        <v>5.885000000000002</v>
       </c>
       <c r="F46">
-        <v>18.172</v>
+        <v>18.585</v>
       </c>
       <c r="G46">
         <v>1.12</v>
@@ -5047,28 +5047,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M46">
-        <v>0.9867396</v>
+        <v>1.0091655</v>
       </c>
       <c r="N46">
-        <v>6.096729787755102</v>
+        <v>6.074303887755102</v>
       </c>
       <c r="O46">
-        <v>1.707084340571429</v>
+        <v>1.700805088571429</v>
       </c>
       <c r="P46">
-        <v>4.389645447183673</v>
+        <v>4.373498799183674</v>
       </c>
       <c r="Q46">
-        <v>5.479645447183673</v>
+        <v>5.463498799183673</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08250941568886613</v>
+        <v>0.08305749920114183</v>
       </c>
       <c r="T46">
-        <v>0.8477925101354769</v>
+        <v>0.8604503279709432</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.178661308165904</v>
+        <v>7.019135501317773</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06327482456062801</v>
+        <v>0.06314213633549098</v>
       </c>
       <c r="C47">
-        <v>23.71189882224591</v>
+        <v>23.34981572945489</v>
       </c>
       <c r="D47">
-        <v>41.17689882224592</v>
+        <v>41.22781572945489</v>
       </c>
       <c r="E47">
-        <v>5.885000000000002</v>
+        <v>6.298000000000002</v>
       </c>
       <c r="F47">
-        <v>18.585</v>
+        <v>18.998</v>
       </c>
       <c r="G47">
         <v>1.12</v>
@@ -5129,28 +5129,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M47">
-        <v>1.0091655</v>
+        <v>1.0315914</v>
       </c>
       <c r="N47">
-        <v>6.074303887755102</v>
+        <v>6.051877987755102</v>
       </c>
       <c r="O47">
-        <v>1.700805088571429</v>
+        <v>1.694525836571429</v>
       </c>
       <c r="P47">
-        <v>4.373498799183674</v>
+        <v>4.357352151183673</v>
       </c>
       <c r="Q47">
-        <v>5.463498799183673</v>
+        <v>5.447352151183673</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08305749920114183</v>
+        <v>0.08362588210276109</v>
       </c>
       <c r="T47">
-        <v>0.8604503279709432</v>
+        <v>0.8735769538743903</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.019135501317773</v>
+        <v>6.866545599115213</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06314213633549098</v>
+        <v>0.06300944811035397</v>
       </c>
       <c r="C48">
-        <v>23.34981572945489</v>
+        <v>22.98785871420991</v>
       </c>
       <c r="D48">
-        <v>41.22781572945489</v>
+        <v>41.27885871420992</v>
       </c>
       <c r="E48">
-        <v>6.298000000000002</v>
+        <v>6.711000000000002</v>
       </c>
       <c r="F48">
-        <v>18.998</v>
+        <v>19.411</v>
       </c>
       <c r="G48">
         <v>1.12</v>
@@ -5211,28 +5211,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M48">
-        <v>1.0315914</v>
+        <v>1.0540173</v>
       </c>
       <c r="N48">
-        <v>6.051877987755102</v>
+        <v>6.029452087755102</v>
       </c>
       <c r="O48">
-        <v>1.694525836571429</v>
+        <v>1.688246584571429</v>
       </c>
       <c r="P48">
-        <v>4.357352151183673</v>
+        <v>4.341205503183673</v>
       </c>
       <c r="Q48">
-        <v>5.447352151183673</v>
+        <v>5.431205503183673</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08362588210276109</v>
+        <v>0.0842157134157622</v>
       </c>
       <c r="T48">
-        <v>0.8735769538743903</v>
+        <v>0.8871989241515521</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.866545599115213</v>
+        <v>6.720448884240421</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06300944811035397</v>
+        <v>0.06287675988521695</v>
       </c>
       <c r="C49">
-        <v>22.98785871420991</v>
+        <v>22.62602824537055</v>
       </c>
       <c r="D49">
-        <v>41.27885871420992</v>
+        <v>41.33002824537056</v>
       </c>
       <c r="E49">
-        <v>6.711000000000002</v>
+        <v>7.124000000000002</v>
       </c>
       <c r="F49">
-        <v>19.411</v>
+        <v>19.824</v>
       </c>
       <c r="G49">
         <v>1.12</v>
@@ -5293,28 +5293,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M49">
-        <v>1.0540173</v>
+        <v>1.0764432</v>
       </c>
       <c r="N49">
-        <v>6.029452087755102</v>
+        <v>6.007026187755102</v>
       </c>
       <c r="O49">
-        <v>1.688246584571429</v>
+        <v>1.681967332571429</v>
       </c>
       <c r="P49">
-        <v>4.341205503183673</v>
+        <v>4.325058855183674</v>
       </c>
       <c r="Q49">
-        <v>5.431205503183673</v>
+        <v>5.415058855183673</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0842157134157622</v>
+        <v>0.08482823054849412</v>
       </c>
       <c r="T49">
-        <v>0.8871989241515521</v>
+        <v>0.901344816362451</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.720448884240421</v>
+        <v>6.580439532485412</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06287675988521693</v>
+        <v>0.06274407166007992</v>
       </c>
       <c r="C50">
-        <v>22.62602824537056</v>
+        <v>22.26432479412404</v>
       </c>
       <c r="D50">
-        <v>41.33002824537056</v>
+        <v>41.38132479412404</v>
       </c>
       <c r="E50">
-        <v>7.123999999999999</v>
+        <v>7.536999999999999</v>
       </c>
       <c r="F50">
-        <v>19.824</v>
+        <v>20.237</v>
       </c>
       <c r="G50">
         <v>1.12</v>
@@ -5375,28 +5375,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M50">
-        <v>1.0764432</v>
+        <v>1.0988691</v>
       </c>
       <c r="N50">
-        <v>6.007026187755102</v>
+        <v>5.984600287755102</v>
       </c>
       <c r="O50">
-        <v>1.681967332571429</v>
+        <v>1.675688080571429</v>
       </c>
       <c r="P50">
-        <v>4.325058855183674</v>
+        <v>4.308912207183673</v>
       </c>
       <c r="Q50">
-        <v>5.415058855183673</v>
+        <v>5.398912207183673</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08482823054849412</v>
+        <v>0.08546476796094102</v>
       </c>
       <c r="T50">
-        <v>0.9013448163624509</v>
+        <v>0.9160454494443654</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.580439532485413</v>
+        <v>6.446144848148976</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06274407166007992</v>
+        <v>0.06261138343494289</v>
       </c>
       <c r="C51">
-        <v>22.26432479412404</v>
+        <v>21.90274883399975</v>
       </c>
       <c r="D51">
-        <v>41.38132479412404</v>
+        <v>41.43274883399975</v>
       </c>
       <c r="E51">
-        <v>7.536999999999999</v>
+        <v>7.949999999999999</v>
       </c>
       <c r="F51">
-        <v>20.237</v>
+        <v>20.65</v>
       </c>
       <c r="G51">
         <v>1.12</v>
@@ -5457,28 +5457,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M51">
-        <v>1.0988691</v>
+        <v>1.121295</v>
       </c>
       <c r="N51">
-        <v>5.984600287755102</v>
+        <v>5.962174387755102</v>
       </c>
       <c r="O51">
-        <v>1.675688080571429</v>
+        <v>1.669408828571429</v>
       </c>
       <c r="P51">
-        <v>4.308912207183673</v>
+        <v>4.292765559183673</v>
       </c>
       <c r="Q51">
-        <v>5.398912207183673</v>
+        <v>5.382765559183673</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08546476796094102</v>
+        <v>0.0861267668698858</v>
       </c>
       <c r="T51">
-        <v>0.9160454494443654</v>
+        <v>0.9313341078495566</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.446144848148976</v>
+        <v>6.317221951185997</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06261138343494289</v>
+        <v>0.06247869520980587</v>
       </c>
       <c r="C52">
-        <v>21.90274883399975</v>
+        <v>21.5413008408838</v>
       </c>
       <c r="D52">
-        <v>41.43274883399975</v>
+        <v>41.4843008408838</v>
       </c>
       <c r="E52">
-        <v>7.949999999999999</v>
+        <v>8.363</v>
       </c>
       <c r="F52">
-        <v>20.65</v>
+        <v>21.063</v>
       </c>
       <c r="G52">
         <v>1.12</v>
@@ -5539,28 +5539,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M52">
-        <v>1.121295</v>
+        <v>1.1437209</v>
       </c>
       <c r="N52">
-        <v>5.962174387755102</v>
+        <v>5.939748487755102</v>
       </c>
       <c r="O52">
-        <v>1.669408828571429</v>
+        <v>1.663129576571429</v>
       </c>
       <c r="P52">
-        <v>4.292765559183673</v>
+        <v>4.276618911183673</v>
       </c>
       <c r="Q52">
-        <v>5.382765559183673</v>
+        <v>5.366618911183673</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0861267668698858</v>
+        <v>0.08681578614246097</v>
       </c>
       <c r="T52">
-        <v>0.9313341078495566</v>
+        <v>0.947246793128429</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.317221951185997</v>
+        <v>6.193354854103919</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06247869520980587</v>
+        <v>0.06272040698466885</v>
       </c>
       <c r="C53">
-        <v>21.5413008408838</v>
+        <v>21.03448681223608</v>
       </c>
       <c r="D53">
-        <v>41.4843008408838</v>
+        <v>41.39048681223608</v>
       </c>
       <c r="E53">
-        <v>8.363</v>
+        <v>8.776</v>
       </c>
       <c r="F53">
-        <v>21.063</v>
+        <v>21.476</v>
       </c>
       <c r="G53">
         <v>1.12</v>
@@ -5621,45 +5621,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M53">
-        <v>1.1437209</v>
+        <v>1.1876228</v>
       </c>
       <c r="N53">
-        <v>5.939748487755102</v>
+        <v>5.895846587755102</v>
       </c>
       <c r="O53">
-        <v>1.663129576571429</v>
+        <v>1.650837044571429</v>
       </c>
       <c r="P53">
-        <v>4.276618911183673</v>
+        <v>4.245009543183674</v>
       </c>
       <c r="Q53">
-        <v>5.366618911183673</v>
+        <v>5.335009543183673</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08681578614246097</v>
+        <v>0.08753351455139344</v>
       </c>
       <c r="T53">
-        <v>0.947246793128429</v>
+        <v>0.9638225069605876</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.28</v>
       </c>
       <c r="W53">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.193354854103919</v>
+        <v>5.964410070061893</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06272040698466885</v>
+        <v>0.06259491875953183</v>
       </c>
       <c r="C54">
-        <v>21.03448681223608</v>
+        <v>20.67013872294764</v>
       </c>
       <c r="D54">
-        <v>41.39048681223608</v>
+        <v>41.43913872294764</v>
       </c>
       <c r="E54">
-        <v>8.776</v>
+        <v>9.189</v>
       </c>
       <c r="F54">
-        <v>21.476</v>
+        <v>21.889</v>
       </c>
       <c r="G54">
         <v>1.12</v>
@@ -5703,28 +5703,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M54">
-        <v>1.1876228</v>
+        <v>1.2104617</v>
       </c>
       <c r="N54">
-        <v>5.895846587755102</v>
+        <v>5.873007687755102</v>
       </c>
       <c r="O54">
-        <v>1.650837044571429</v>
+        <v>1.644442152571429</v>
       </c>
       <c r="P54">
-        <v>4.245009543183674</v>
+        <v>4.228565535183673</v>
       </c>
       <c r="Q54">
-        <v>5.335009543183673</v>
+        <v>5.318565535183673</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08753351455139344</v>
+        <v>0.08828178459474857</v>
       </c>
       <c r="T54">
-        <v>0.9638225069605876</v>
+        <v>0.9811035703175192</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.964410070061893</v>
+        <v>5.851874031004122</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06259491875953183</v>
+        <v>0.06246943053439481</v>
       </c>
       <c r="C55">
-        <v>20.67013872294764</v>
+        <v>20.3059051427719</v>
       </c>
       <c r="D55">
-        <v>41.43913872294764</v>
+        <v>41.4879051427719</v>
       </c>
       <c r="E55">
-        <v>9.189</v>
+        <v>9.602</v>
       </c>
       <c r="F55">
-        <v>21.889</v>
+        <v>22.302</v>
       </c>
       <c r="G55">
         <v>1.12</v>
@@ -5785,28 +5785,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M55">
-        <v>1.2104617</v>
+        <v>1.2333006</v>
       </c>
       <c r="N55">
-        <v>5.873007687755102</v>
+        <v>5.850168787755102</v>
       </c>
       <c r="O55">
-        <v>1.644442152571429</v>
+        <v>1.638047260571429</v>
       </c>
       <c r="P55">
-        <v>4.228565535183673</v>
+        <v>4.212121527183673</v>
       </c>
       <c r="Q55">
-        <v>5.318565535183673</v>
+        <v>5.302121527183673</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08828178459474857</v>
+        <v>0.08906258811824957</v>
       </c>
       <c r="T55">
-        <v>0.9811035703175192</v>
+        <v>0.9991359842551867</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.851874031004122</v>
+        <v>5.743505993392935</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06246943053439481</v>
+        <v>0.06234394230925777</v>
       </c>
       <c r="C56">
-        <v>20.3059051427719</v>
+        <v>19.94178647645512</v>
       </c>
       <c r="D56">
-        <v>41.4879051427719</v>
+        <v>41.53678647645512</v>
       </c>
       <c r="E56">
-        <v>9.602</v>
+        <v>10.015</v>
       </c>
       <c r="F56">
-        <v>22.302</v>
+        <v>22.715</v>
       </c>
       <c r="G56">
         <v>1.12</v>
@@ -5867,28 +5867,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M56">
-        <v>1.2333006</v>
+        <v>1.2561395</v>
       </c>
       <c r="N56">
-        <v>5.850168787755102</v>
+        <v>5.827329887755102</v>
       </c>
       <c r="O56">
-        <v>1.638047260571429</v>
+        <v>1.631652368571429</v>
       </c>
       <c r="P56">
-        <v>4.212121527183673</v>
+        <v>4.195677519183674</v>
       </c>
       <c r="Q56">
-        <v>5.302121527183673</v>
+        <v>5.285677519183674</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08906258811824957</v>
+        <v>0.08987809402057284</v>
       </c>
       <c r="T56">
-        <v>0.9991359842551867</v>
+        <v>1.017969838812306</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.743505993392935</v>
+        <v>5.639078611694881</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06234394230925777</v>
+        <v>0.06221845408412076</v>
       </c>
       <c r="C57">
-        <v>19.94178647645512</v>
+        <v>19.57778313065329</v>
       </c>
       <c r="D57">
-        <v>41.53678647645512</v>
+        <v>41.5857831306533</v>
       </c>
       <c r="E57">
-        <v>10.015</v>
+        <v>10.428</v>
       </c>
       <c r="F57">
-        <v>22.715</v>
+        <v>23.128</v>
       </c>
       <c r="G57">
         <v>1.12</v>
@@ -5949,28 +5949,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M57">
-        <v>1.2561395</v>
+        <v>1.2789784</v>
       </c>
       <c r="N57">
-        <v>5.827329887755102</v>
+        <v>5.804490987755102</v>
       </c>
       <c r="O57">
-        <v>1.631652368571429</v>
+        <v>1.625257476571429</v>
       </c>
       <c r="P57">
-        <v>4.195677519183674</v>
+        <v>4.179233511183673</v>
       </c>
       <c r="Q57">
-        <v>5.285677519183674</v>
+        <v>5.269233511183673</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08987809402057284</v>
+        <v>0.09073066837300173</v>
       </c>
       <c r="T57">
-        <v>1.017969838812306</v>
+        <v>1.037659777667477</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.639078611694881</v>
+        <v>5.538380779343187</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06221845408412076</v>
+        <v>0.06209296585898373</v>
       </c>
       <c r="C58">
-        <v>19.57778313065329</v>
+        <v>19.21389551394348</v>
       </c>
       <c r="D58">
-        <v>41.5857831306533</v>
+        <v>41.63489551394348</v>
       </c>
       <c r="E58">
-        <v>10.428</v>
+        <v>10.841</v>
       </c>
       <c r="F58">
-        <v>23.128</v>
+        <v>23.541</v>
       </c>
       <c r="G58">
         <v>1.12</v>
@@ -6031,28 +6031,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M58">
-        <v>1.2789784</v>
+        <v>1.3018173</v>
       </c>
       <c r="N58">
-        <v>5.804490987755102</v>
+        <v>5.781652087755102</v>
       </c>
       <c r="O58">
-        <v>1.625257476571429</v>
+        <v>1.618862584571429</v>
       </c>
       <c r="P58">
-        <v>4.179233511183673</v>
+        <v>4.162789503183673</v>
       </c>
       <c r="Q58">
-        <v>5.269233511183673</v>
+        <v>5.252789503183673</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09073066837300173</v>
+        <v>0.0916228973464738</v>
       </c>
       <c r="T58">
-        <v>1.037659777667477</v>
+        <v>1.05826552763219</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.538380779343187</v>
+        <v>5.441216204266991</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06209296585898373</v>
+        <v>0.0619674776338467</v>
       </c>
       <c r="C59">
-        <v>19.21389551394348</v>
+        <v>18.85012403683509</v>
       </c>
       <c r="D59">
-        <v>41.63489551394348</v>
+        <v>41.68412403683509</v>
       </c>
       <c r="E59">
-        <v>10.841</v>
+        <v>11.254</v>
       </c>
       <c r="F59">
-        <v>23.541</v>
+        <v>23.954</v>
       </c>
       <c r="G59">
         <v>1.12</v>
@@ -6113,28 +6113,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M59">
-        <v>1.3018173</v>
+        <v>1.3246562</v>
       </c>
       <c r="N59">
-        <v>5.781652087755102</v>
+        <v>5.758813187755102</v>
       </c>
       <c r="O59">
-        <v>1.618862584571429</v>
+        <v>1.612467692571429</v>
       </c>
       <c r="P59">
-        <v>4.162789503183673</v>
+        <v>4.146345495183674</v>
       </c>
       <c r="Q59">
-        <v>5.252789503183673</v>
+        <v>5.236345495183674</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.0916228973464738</v>
+        <v>0.09255761341392074</v>
       </c>
       <c r="T59">
-        <v>1.05826552763219</v>
+        <v>1.079852503785699</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.441216204266991</v>
+        <v>5.347402131779628</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06196747763384672</v>
+        <v>0.06184198940870969</v>
       </c>
       <c r="C60">
-        <v>18.85012403683508</v>
+        <v>18.48646911178135</v>
       </c>
       <c r="D60">
-        <v>41.68412403683508</v>
+        <v>41.73346911178135</v>
       </c>
       <c r="E60">
-        <v>11.254</v>
+        <v>11.667</v>
       </c>
       <c r="F60">
-        <v>23.954</v>
+        <v>24.367</v>
       </c>
       <c r="G60">
         <v>1.12</v>
@@ -6195,28 +6195,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M60">
-        <v>1.3246562</v>
+        <v>1.3474951</v>
       </c>
       <c r="N60">
-        <v>5.758813187755102</v>
+        <v>5.735974287755102</v>
       </c>
       <c r="O60">
-        <v>1.612467692571429</v>
+        <v>1.606072800571429</v>
       </c>
       <c r="P60">
-        <v>4.146345495183674</v>
+        <v>4.129901487183673</v>
       </c>
       <c r="Q60">
-        <v>5.236345495183674</v>
+        <v>5.219901487183673</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09255761341392074</v>
+        <v>0.09353792538709679</v>
       </c>
       <c r="T60">
-        <v>1.079852503785699</v>
+        <v>1.102492503166208</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.347402131779629</v>
+        <v>5.256768197342686</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06184198940870969</v>
+        <v>0.06171650118357266</v>
       </c>
       <c r="C61">
-        <v>18.48646911178135</v>
+        <v>18.12293115319085</v>
       </c>
       <c r="D61">
-        <v>41.73346911178135</v>
+        <v>41.78293115319085</v>
       </c>
       <c r="E61">
-        <v>11.667</v>
+        <v>12.08</v>
       </c>
       <c r="F61">
-        <v>24.367</v>
+        <v>24.78</v>
       </c>
       <c r="G61">
         <v>1.12</v>
@@ -6277,28 +6277,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M61">
-        <v>1.3474951</v>
+        <v>1.370334</v>
       </c>
       <c r="N61">
-        <v>5.735974287755102</v>
+        <v>5.713135387755102</v>
       </c>
       <c r="O61">
-        <v>1.606072800571429</v>
+        <v>1.599677908571429</v>
       </c>
       <c r="P61">
-        <v>4.129901487183673</v>
+        <v>4.113457479183674</v>
       </c>
       <c r="Q61">
-        <v>5.219901487183673</v>
+        <v>5.203457479183673</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09353792538709679</v>
+        <v>0.09456725295893166</v>
       </c>
       <c r="T61">
-        <v>1.102492503166208</v>
+        <v>1.126264502515743</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.256768197342686</v>
+        <v>5.169155394053641</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06171650118357266</v>
+        <v>0.06159101295843564</v>
       </c>
       <c r="C62">
-        <v>18.12293115319085</v>
+        <v>17.75951057743911</v>
       </c>
       <c r="D62">
-        <v>41.78293115319085</v>
+        <v>41.83251057743911</v>
       </c>
       <c r="E62">
-        <v>12.08</v>
+        <v>12.493</v>
       </c>
       <c r="F62">
-        <v>24.78</v>
+        <v>25.193</v>
       </c>
       <c r="G62">
         <v>1.12</v>
@@ -6359,28 +6359,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M62">
-        <v>1.370334</v>
+        <v>1.3931729</v>
       </c>
       <c r="N62">
-        <v>5.713135387755102</v>
+        <v>5.690296487755102</v>
       </c>
       <c r="O62">
-        <v>1.599677908571429</v>
+        <v>1.593283016571429</v>
       </c>
       <c r="P62">
-        <v>4.113457479183674</v>
+        <v>4.097013471183674</v>
       </c>
       <c r="Q62">
-        <v>5.203457479183673</v>
+        <v>5.187013471183674</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09456725295893166</v>
+        <v>0.09564936656009138</v>
       </c>
       <c r="T62">
-        <v>1.126264502515743</v>
+        <v>1.151255578754997</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.169155394053641</v>
+        <v>5.084415141692106</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06159101295843564</v>
+        <v>0.06146552473329861</v>
       </c>
       <c r="C63">
-        <v>17.75951057743911</v>
+        <v>17.39620780288028</v>
       </c>
       <c r="D63">
-        <v>41.83251057743911</v>
+        <v>41.88220780288028</v>
       </c>
       <c r="E63">
-        <v>12.493</v>
+        <v>12.906</v>
       </c>
       <c r="F63">
-        <v>25.193</v>
+        <v>25.606</v>
       </c>
       <c r="G63">
         <v>1.12</v>
@@ -6441,28 +6441,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M63">
-        <v>1.3931729</v>
+        <v>1.4160118</v>
       </c>
       <c r="N63">
-        <v>5.690296487755102</v>
+        <v>5.667457587755102</v>
       </c>
       <c r="O63">
-        <v>1.593283016571429</v>
+        <v>1.586888124571429</v>
       </c>
       <c r="P63">
-        <v>4.097013471183674</v>
+        <v>4.080569463183673</v>
       </c>
       <c r="Q63">
-        <v>5.187013471183674</v>
+        <v>5.170569463183673</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09564936656009138</v>
+        <v>0.09678843350868058</v>
       </c>
       <c r="T63">
-        <v>1.151255578754997</v>
+        <v>1.177561974796318</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.084415141692106</v>
+        <v>5.002408445858363</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06146552473329861</v>
+        <v>0.0613400365081616</v>
       </c>
       <c r="C64">
-        <v>17.39620780288028</v>
+        <v>17.03302324985888</v>
       </c>
       <c r="D64">
-        <v>41.88220780288028</v>
+        <v>41.93202324985888</v>
       </c>
       <c r="E64">
-        <v>12.906</v>
+        <v>13.319</v>
       </c>
       <c r="F64">
-        <v>25.606</v>
+        <v>26.019</v>
       </c>
       <c r="G64">
         <v>1.12</v>
@@ -6523,28 +6523,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M64">
-        <v>1.4160118</v>
+        <v>1.4388507</v>
       </c>
       <c r="N64">
-        <v>5.667457587755102</v>
+        <v>5.644618687755102</v>
       </c>
       <c r="O64">
-        <v>1.586888124571429</v>
+        <v>1.580493232571429</v>
       </c>
       <c r="P64">
-        <v>4.080569463183673</v>
+        <v>4.064125455183674</v>
       </c>
       <c r="Q64">
-        <v>5.170569463183673</v>
+        <v>5.154125455183673</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09678843350868058</v>
+        <v>0.09798907164367998</v>
       </c>
       <c r="T64">
-        <v>1.177561974796318</v>
+        <v>1.205290338191224</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.002408445858363</v>
+        <v>4.923005137193944</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0613400365081616</v>
+        <v>0.06121454828302457</v>
       </c>
       <c r="C65">
-        <v>17.03302324985888</v>
+        <v>16.66995734072171</v>
       </c>
       <c r="D65">
-        <v>41.93202324985888</v>
+        <v>41.98195734072171</v>
       </c>
       <c r="E65">
-        <v>13.319</v>
+        <v>13.732</v>
       </c>
       <c r="F65">
-        <v>26.019</v>
+        <v>26.432</v>
       </c>
       <c r="G65">
         <v>1.12</v>
@@ -6605,28 +6605,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M65">
-        <v>1.4388507</v>
+        <v>1.4616896</v>
       </c>
       <c r="N65">
-        <v>5.644618687755102</v>
+        <v>5.621779787755102</v>
       </c>
       <c r="O65">
-        <v>1.580493232571429</v>
+        <v>1.574098340571429</v>
       </c>
       <c r="P65">
-        <v>4.064125455183674</v>
+        <v>4.047681447183673</v>
       </c>
       <c r="Q65">
-        <v>5.154125455183673</v>
+        <v>5.137681447183673</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09798907164367998</v>
+        <v>0.09925641189729048</v>
       </c>
       <c r="T65">
-        <v>1.205290338191224</v>
+        <v>1.23455916621918</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.923005137193944</v>
+        <v>4.846083181925289</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06121454828302457</v>
+        <v>0.06108906005788754</v>
       </c>
       <c r="C66">
-        <v>16.66995734072171</v>
+        <v>16.30701049982972</v>
       </c>
       <c r="D66">
-        <v>41.98195734072171</v>
+        <v>42.03201049982972</v>
       </c>
       <c r="E66">
-        <v>13.732</v>
+        <v>14.145</v>
       </c>
       <c r="F66">
-        <v>26.432</v>
+        <v>26.845</v>
       </c>
       <c r="G66">
         <v>1.12</v>
@@ -6687,28 +6687,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M66">
-        <v>1.4616896</v>
+        <v>1.4845285</v>
       </c>
       <c r="N66">
-        <v>5.621779787755102</v>
+        <v>5.598940887755102</v>
       </c>
       <c r="O66">
-        <v>1.574098340571429</v>
+        <v>1.567703448571429</v>
       </c>
       <c r="P66">
-        <v>4.047681447183673</v>
+        <v>4.031237439183673</v>
       </c>
       <c r="Q66">
-        <v>5.137681447183673</v>
+        <v>5.121237439183673</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09925641189729048</v>
+        <v>0.1005961715939644</v>
       </c>
       <c r="T66">
-        <v>1.23455916621918</v>
+        <v>1.265500498705876</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.846083181925289</v>
+        <v>4.771528056049515</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06108906005788754</v>
+        <v>0.06096357183275052</v>
       </c>
       <c r="C67">
-        <v>16.30701049982972</v>
+        <v>15.94418315357006</v>
       </c>
       <c r="D67">
-        <v>42.03201049982972</v>
+        <v>42.08218315357006</v>
       </c>
       <c r="E67">
-        <v>14.145</v>
+        <v>14.558</v>
       </c>
       <c r="F67">
-        <v>26.845</v>
+        <v>27.258</v>
       </c>
       <c r="G67">
         <v>1.12</v>
@@ -6769,28 +6769,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M67">
-        <v>1.4845285</v>
+        <v>1.5073674</v>
       </c>
       <c r="N67">
-        <v>5.598940887755102</v>
+        <v>5.576101987755102</v>
       </c>
       <c r="O67">
-        <v>1.567703448571429</v>
+        <v>1.561308556571429</v>
       </c>
       <c r="P67">
-        <v>4.031237439183673</v>
+        <v>4.014793431183674</v>
       </c>
       <c r="Q67">
-        <v>5.121237439183673</v>
+        <v>5.104793431183674</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1005961715939644</v>
+        <v>0.1020147406845603</v>
       </c>
       <c r="T67">
-        <v>1.265500498705876</v>
+        <v>1.298261909574142</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.771528056049515</v>
+        <v>4.699232176412401</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06096357183275052</v>
+        <v>0.0608380836076135</v>
       </c>
       <c r="C68">
-        <v>15.94418315357006</v>
+        <v>15.5814757303682</v>
       </c>
       <c r="D68">
-        <v>42.08218315357006</v>
+        <v>42.13247573036821</v>
       </c>
       <c r="E68">
-        <v>14.558</v>
+        <v>14.971</v>
       </c>
       <c r="F68">
-        <v>27.258</v>
+        <v>27.671</v>
       </c>
       <c r="G68">
         <v>1.12</v>
@@ -6851,28 +6851,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M68">
-        <v>1.5073674</v>
+        <v>1.5302063</v>
       </c>
       <c r="N68">
-        <v>5.576101987755102</v>
+        <v>5.553263087755102</v>
       </c>
       <c r="O68">
-        <v>1.561308556571429</v>
+        <v>1.554913664571429</v>
       </c>
       <c r="P68">
-        <v>4.014793431183674</v>
+        <v>3.998349423183673</v>
       </c>
       <c r="Q68">
-        <v>5.104793431183674</v>
+        <v>5.088349423183673</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1020147406845603</v>
+        <v>0.1035192836594349</v>
       </c>
       <c r="T68">
-        <v>1.298261909574142</v>
+        <v>1.333008860495031</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.699232176412401</v>
+        <v>4.629094382734604</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0608380836076135</v>
+        <v>0.06071259538247648</v>
       </c>
       <c r="C69">
-        <v>15.5814757303682</v>
+        <v>15.21888866070013</v>
       </c>
       <c r="D69">
-        <v>42.13247573036821</v>
+        <v>42.18288866070013</v>
       </c>
       <c r="E69">
-        <v>14.971</v>
+        <v>15.384</v>
       </c>
       <c r="F69">
-        <v>27.671</v>
+        <v>28.084</v>
       </c>
       <c r="G69">
         <v>1.12</v>
@@ -6933,28 +6933,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M69">
-        <v>1.5302063</v>
+        <v>1.5530452</v>
       </c>
       <c r="N69">
-        <v>5.553263087755102</v>
+        <v>5.530424187755102</v>
       </c>
       <c r="O69">
-        <v>1.554913664571429</v>
+        <v>1.548518772571429</v>
       </c>
       <c r="P69">
-        <v>3.998349423183673</v>
+        <v>3.981905415183673</v>
       </c>
       <c r="Q69">
-        <v>5.088349423183673</v>
+        <v>5.071905415183673</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1035192836594349</v>
+        <v>0.105117860570239</v>
       </c>
       <c r="T69">
-        <v>1.333008860495031</v>
+        <v>1.369927495848476</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.629094382734604</v>
+        <v>4.561019465341447</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06071259538247648</v>
+        <v>0.06182910715733946</v>
       </c>
       <c r="C70">
-        <v>15.21888866070013</v>
+        <v>14.36154134475898</v>
       </c>
       <c r="D70">
-        <v>42.18288866070013</v>
+        <v>41.73854134475899</v>
       </c>
       <c r="E70">
-        <v>15.384</v>
+        <v>15.797</v>
       </c>
       <c r="F70">
-        <v>28.084</v>
+        <v>28.497</v>
       </c>
       <c r="G70">
         <v>1.12</v>
@@ -7015,45 +7015,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M70">
-        <v>1.5530452</v>
+        <v>1.6471266</v>
       </c>
       <c r="N70">
-        <v>5.530424187755102</v>
+        <v>5.436342787755102</v>
       </c>
       <c r="O70">
-        <v>1.548518772571429</v>
+        <v>1.522175980571429</v>
       </c>
       <c r="P70">
-        <v>3.981905415183673</v>
+        <v>3.914166807183673</v>
       </c>
       <c r="Q70">
-        <v>5.071905415183673</v>
+        <v>5.004166807183673</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.105117860570239</v>
+        <v>0.1068195714752886</v>
       </c>
       <c r="T70">
-        <v>1.369927495848476</v>
+        <v>1.409227978644078</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.28</v>
       </c>
       <c r="W70">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.561019465341447</v>
+        <v>4.30050087695451</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06182910715733946</v>
+        <v>0.06172161893220243</v>
       </c>
       <c r="C71">
-        <v>14.36154134475898</v>
+        <v>13.99091166445313</v>
       </c>
       <c r="D71">
-        <v>41.73854134475899</v>
+        <v>41.78091166445313</v>
       </c>
       <c r="E71">
-        <v>15.797</v>
+        <v>16.21</v>
       </c>
       <c r="F71">
-        <v>28.497</v>
+        <v>28.91</v>
       </c>
       <c r="G71">
         <v>1.12</v>
@@ -7097,28 +7097,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M71">
-        <v>1.6471266</v>
+        <v>1.670998</v>
       </c>
       <c r="N71">
-        <v>5.436342787755102</v>
+        <v>5.412471387755102</v>
       </c>
       <c r="O71">
-        <v>1.522175980571429</v>
+        <v>1.515491988571429</v>
       </c>
       <c r="P71">
-        <v>3.914166807183673</v>
+        <v>3.896979399183673</v>
       </c>
       <c r="Q71">
-        <v>5.004166807183673</v>
+        <v>4.986979399183673</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1068195714752886</v>
+        <v>0.1086347297740081</v>
       </c>
       <c r="T71">
-        <v>1.409227978644078</v>
+        <v>1.451148493626054</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.30050087695451</v>
+        <v>4.239065150140874</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06172161893220243</v>
+        <v>0.06161413070706541</v>
       </c>
       <c r="C72">
-        <v>13.99091166445313</v>
+        <v>13.62036809488342</v>
       </c>
       <c r="D72">
-        <v>41.78091166445313</v>
+        <v>41.82336809488342</v>
       </c>
       <c r="E72">
-        <v>16.21</v>
+        <v>16.623</v>
       </c>
       <c r="F72">
-        <v>28.91</v>
+        <v>29.323</v>
       </c>
       <c r="G72">
         <v>1.12</v>
@@ -7179,28 +7179,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M72">
-        <v>1.670998</v>
+        <v>1.6948694</v>
       </c>
       <c r="N72">
-        <v>5.412471387755102</v>
+        <v>5.388599987755102</v>
       </c>
       <c r="O72">
-        <v>1.515491988571429</v>
+        <v>1.508807996571429</v>
       </c>
       <c r="P72">
-        <v>3.896979399183673</v>
+        <v>3.879791991183673</v>
       </c>
       <c r="Q72">
-        <v>4.986979399183673</v>
+        <v>4.969791991183673</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1086347297740081</v>
+        <v>0.1105750714036738</v>
       </c>
       <c r="T72">
-        <v>1.451148493626054</v>
+        <v>1.495960078606786</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.239065150140874</v>
+        <v>4.179360007181144</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06161413070706541</v>
+        <v>0.06150664248192839</v>
       </c>
       <c r="C73">
-        <v>13.62036809488342</v>
+        <v>13.24991089882586</v>
       </c>
       <c r="D73">
-        <v>41.82336809488342</v>
+        <v>41.86591089882586</v>
       </c>
       <c r="E73">
-        <v>16.623</v>
+        <v>17.036</v>
       </c>
       <c r="F73">
-        <v>29.323</v>
+        <v>29.736</v>
       </c>
       <c r="G73">
         <v>1.12</v>
@@ -7261,28 +7261,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M73">
-        <v>1.6948694</v>
+        <v>1.7187408</v>
       </c>
       <c r="N73">
-        <v>5.388599987755102</v>
+        <v>5.364728587755102</v>
       </c>
       <c r="O73">
-        <v>1.508807996571429</v>
+        <v>1.502124004571429</v>
       </c>
       <c r="P73">
-        <v>3.879791991183673</v>
+        <v>3.862604583183673</v>
       </c>
       <c r="Q73">
-        <v>4.969791991183673</v>
+        <v>4.952604583183673</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1105750714036738</v>
+        <v>0.1126540088640299</v>
       </c>
       <c r="T73">
-        <v>1.495960078606786</v>
+        <v>1.543972491086142</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.179360007181145</v>
+        <v>4.12131334041474</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06150664248192839</v>
+        <v>0.06139915425679136</v>
       </c>
       <c r="C74">
-        <v>13.24991089882586</v>
+        <v>12.87954034012668</v>
       </c>
       <c r="D74">
-        <v>41.86591089882586</v>
+        <v>41.90854034012668</v>
       </c>
       <c r="E74">
-        <v>17.036</v>
+        <v>17.449</v>
       </c>
       <c r="F74">
-        <v>29.736</v>
+        <v>30.149</v>
       </c>
       <c r="G74">
         <v>1.12</v>
@@ -7343,28 +7343,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M74">
-        <v>1.7187408</v>
+        <v>1.7426122</v>
       </c>
       <c r="N74">
-        <v>5.364728587755102</v>
+        <v>5.340857187755102</v>
       </c>
       <c r="O74">
-        <v>1.502124004571429</v>
+        <v>1.495440012571429</v>
       </c>
       <c r="P74">
-        <v>3.862604583183673</v>
+        <v>3.845417175183673</v>
       </c>
       <c r="Q74">
-        <v>4.952604583183673</v>
+        <v>4.935417175183673</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1126540088640299</v>
+        <v>0.1148869416918198</v>
       </c>
       <c r="T74">
-        <v>1.543972491086142</v>
+        <v>1.595541378563969</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.12131334041474</v>
+        <v>4.064856993285771</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06139915425679136</v>
+        <v>0.06129166603165434</v>
       </c>
       <c r="C75">
-        <v>12.87954034012668</v>
+        <v>12.50925668370788</v>
       </c>
       <c r="D75">
-        <v>41.90854034012668</v>
+        <v>41.95125668370788</v>
       </c>
       <c r="E75">
-        <v>17.449</v>
+        <v>17.862</v>
       </c>
       <c r="F75">
-        <v>30.149</v>
+        <v>30.562</v>
       </c>
       <c r="G75">
         <v>1.12</v>
@@ -7425,28 +7425,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M75">
-        <v>1.7426122</v>
+        <v>1.7664836</v>
       </c>
       <c r="N75">
-        <v>5.340857187755102</v>
+        <v>5.316985787755102</v>
       </c>
       <c r="O75">
-        <v>1.495440012571429</v>
+        <v>1.488756020571429</v>
       </c>
       <c r="P75">
-        <v>3.845417175183673</v>
+        <v>3.828229767183673</v>
       </c>
       <c r="Q75">
-        <v>4.935417175183673</v>
+        <v>4.918229767183673</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1148869416918198</v>
+        <v>0.1172916385832859</v>
       </c>
       <c r="T75">
-        <v>1.595541378563969</v>
+        <v>1.65107710354009</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.064856993285771</v>
+        <v>4.009926493376503</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06129166603165434</v>
+        <v>0.06307417780651731</v>
       </c>
       <c r="C76">
-        <v>12.50925668370788</v>
+        <v>11.39894248152389</v>
       </c>
       <c r="D76">
-        <v>41.95125668370788</v>
+        <v>41.25394248152389</v>
       </c>
       <c r="E76">
-        <v>17.862</v>
+        <v>18.275</v>
       </c>
       <c r="F76">
-        <v>30.562</v>
+        <v>30.975</v>
       </c>
       <c r="G76">
         <v>1.12</v>
@@ -7507,45 +7507,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M76">
-        <v>1.7664836</v>
+        <v>1.8987675</v>
       </c>
       <c r="N76">
-        <v>5.316985787755102</v>
+        <v>5.184701887755102</v>
       </c>
       <c r="O76">
-        <v>1.488756020571429</v>
+        <v>1.451716528571429</v>
       </c>
       <c r="P76">
-        <v>3.828229767183673</v>
+        <v>3.732985359183673</v>
       </c>
       <c r="Q76">
-        <v>4.918229767183673</v>
+        <v>4.822985359183673</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1172916385832859</v>
+        <v>0.1198887112260693</v>
       </c>
       <c r="T76">
-        <v>1.65107710354009</v>
+        <v>1.711055686514302</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.28</v>
       </c>
       <c r="W76">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.009926493376503</v>
+        <v>3.730561739525825</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06307417780651731</v>
+        <v>0.06299188958138029</v>
       </c>
       <c r="C77">
-        <v>11.39894248152389</v>
+        <v>11.01762266311526</v>
       </c>
       <c r="D77">
-        <v>41.25394248152389</v>
+        <v>41.28562266311526</v>
       </c>
       <c r="E77">
-        <v>18.275</v>
+        <v>18.688</v>
       </c>
       <c r="F77">
-        <v>30.975</v>
+        <v>31.388</v>
       </c>
       <c r="G77">
         <v>1.12</v>
@@ -7589,28 +7589,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M77">
-        <v>1.8987675</v>
+        <v>1.9240844</v>
       </c>
       <c r="N77">
-        <v>5.184701887755102</v>
+        <v>5.159384987755102</v>
       </c>
       <c r="O77">
-        <v>1.451716528571429</v>
+        <v>1.444627796571429</v>
       </c>
       <c r="P77">
-        <v>3.732985359183673</v>
+        <v>3.714757191183673</v>
       </c>
       <c r="Q77">
-        <v>4.822985359183673</v>
+        <v>4.804757191183673</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1198887112260693</v>
+        <v>0.1227022065890845</v>
       </c>
       <c r="T77">
-        <v>1.711055686514302</v>
+        <v>1.776032484736364</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.730561739525825</v>
+        <v>3.681475400847854</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06299188958138029</v>
+        <v>0.06290960135624327</v>
       </c>
       <c r="C78">
-        <v>11.01762266311526</v>
+        <v>10.63635153848759</v>
       </c>
       <c r="D78">
-        <v>41.28562266311526</v>
+        <v>41.31735153848759</v>
       </c>
       <c r="E78">
-        <v>18.688</v>
+        <v>19.101</v>
       </c>
       <c r="F78">
-        <v>31.388</v>
+        <v>31.801</v>
       </c>
       <c r="G78">
         <v>1.12</v>
@@ -7671,28 +7671,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M78">
-        <v>1.9240844</v>
+        <v>1.9494013</v>
       </c>
       <c r="N78">
-        <v>5.159384987755102</v>
+        <v>5.134068087755102</v>
       </c>
       <c r="O78">
-        <v>1.444627796571429</v>
+        <v>1.437539064571429</v>
       </c>
       <c r="P78">
-        <v>3.714757191183673</v>
+        <v>3.696529023183673</v>
       </c>
       <c r="Q78">
-        <v>4.804757191183673</v>
+        <v>4.786529023183673</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1227022065890845</v>
+        <v>0.1257603537227968</v>
       </c>
       <c r="T78">
-        <v>1.776032484736364</v>
+        <v>1.846659439325562</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.681475400847854</v>
+        <v>3.633664032005674</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06290960135624327</v>
+        <v>0.06282731313110623</v>
       </c>
       <c r="C79">
-        <v>10.63635153848759</v>
+        <v>10.25512921999385</v>
       </c>
       <c r="D79">
-        <v>41.31735153848759</v>
+        <v>41.34912921999385</v>
       </c>
       <c r="E79">
-        <v>19.101</v>
+        <v>19.514</v>
       </c>
       <c r="F79">
-        <v>31.801</v>
+        <v>32.214</v>
       </c>
       <c r="G79">
         <v>1.12</v>
@@ -7753,28 +7753,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M79">
-        <v>1.9494013</v>
+        <v>1.9747182</v>
       </c>
       <c r="N79">
-        <v>5.134068087755102</v>
+        <v>5.108751187755102</v>
       </c>
       <c r="O79">
-        <v>1.437539064571429</v>
+        <v>1.430450332571429</v>
       </c>
       <c r="P79">
-        <v>3.696529023183673</v>
+        <v>3.678300855183673</v>
       </c>
       <c r="Q79">
-        <v>4.786529023183673</v>
+        <v>4.768300855183673</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1257603537227968</v>
+        <v>0.1290965142323011</v>
       </c>
       <c r="T79">
-        <v>1.846659439325562</v>
+        <v>1.923707026150141</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.633664032005674</v>
+        <v>3.587078595697909</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06282731313110623</v>
+        <v>0.06274502490596921</v>
       </c>
       <c r="C80">
-        <v>10.25512921999385</v>
+        <v>9.873955820332881</v>
       </c>
       <c r="D80">
-        <v>41.34912921999385</v>
+        <v>41.38095582033289</v>
       </c>
       <c r="E80">
-        <v>19.514</v>
+        <v>19.927</v>
       </c>
       <c r="F80">
-        <v>32.214</v>
+        <v>32.627</v>
       </c>
       <c r="G80">
         <v>1.12</v>
@@ -7835,28 +7835,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M80">
-        <v>1.9747182</v>
+        <v>2.0000351</v>
       </c>
       <c r="N80">
-        <v>5.108751187755102</v>
+        <v>5.083434287755102</v>
       </c>
       <c r="O80">
-        <v>1.430450332571429</v>
+        <v>1.423361600571429</v>
       </c>
       <c r="P80">
-        <v>3.678300855183673</v>
+        <v>3.660072687183673</v>
       </c>
       <c r="Q80">
-        <v>4.768300855183673</v>
+        <v>4.750072687183673</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1290965142323011</v>
+        <v>0.1327504043141391</v>
       </c>
       <c r="T80">
-        <v>1.923707026150141</v>
+        <v>2.008092478386586</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.587078595697909</v>
+        <v>3.541672537524517</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06274502490596921</v>
+        <v>0.06427553668083219</v>
       </c>
       <c r="C81">
-        <v>9.873955820332881</v>
+        <v>8.876905740684201</v>
       </c>
       <c r="D81">
-        <v>41.38095582033289</v>
+        <v>40.7969057406842</v>
       </c>
       <c r="E81">
-        <v>19.927</v>
+        <v>20.34</v>
       </c>
       <c r="F81">
-        <v>32.627</v>
+        <v>33.04</v>
       </c>
       <c r="G81">
         <v>1.12</v>
@@ -7917,45 +7917,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M81">
-        <v>2.0000351</v>
+        <v>2.117864</v>
       </c>
       <c r="N81">
-        <v>5.083434287755102</v>
+        <v>4.965605387755102</v>
       </c>
       <c r="O81">
-        <v>1.423361600571429</v>
+        <v>1.390369508571429</v>
       </c>
       <c r="P81">
-        <v>3.660072687183673</v>
+        <v>3.575235879183673</v>
       </c>
       <c r="Q81">
-        <v>4.750072687183673</v>
+        <v>4.665235879183673</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1327504043141391</v>
+        <v>0.136769683404161</v>
       </c>
       <c r="T81">
-        <v>2.008092478386586</v>
+        <v>2.100916475846674</v>
       </c>
       <c r="U81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V81">
         <v>0.28</v>
       </c>
       <c r="W81">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.541672537524517</v>
+        <v>3.344629016667313</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06427553668083219</v>
+        <v>0.06421340845569516</v>
       </c>
       <c r="C82">
-        <v>8.876905740684201</v>
+        <v>8.487292926078354</v>
       </c>
       <c r="D82">
-        <v>40.7969057406842</v>
+        <v>40.82029292607836</v>
       </c>
       <c r="E82">
-        <v>20.34</v>
+        <v>20.753</v>
       </c>
       <c r="F82">
-        <v>33.04</v>
+        <v>33.453</v>
       </c>
       <c r="G82">
         <v>1.12</v>
@@ -7999,28 +7999,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M82">
-        <v>2.117864</v>
+        <v>2.1443373</v>
       </c>
       <c r="N82">
-        <v>4.965605387755102</v>
+        <v>4.939132087755102</v>
       </c>
       <c r="O82">
-        <v>1.390369508571429</v>
+        <v>1.382956984571429</v>
       </c>
       <c r="P82">
-        <v>3.575235879183673</v>
+        <v>3.556175103183673</v>
       </c>
       <c r="Q82">
-        <v>4.665235879183673</v>
+        <v>4.646175103183673</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.136769683404161</v>
+        <v>0.1412120445036588</v>
       </c>
       <c r="T82">
-        <v>2.100916475846674</v>
+        <v>2.203511420407825</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.344629016667313</v>
+        <v>3.30333730041216</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06421340845569516</v>
+        <v>0.06415128023055815</v>
       </c>
       <c r="C83">
-        <v>8.487292926078354</v>
+        <v>8.097706940672452</v>
       </c>
       <c r="D83">
-        <v>40.82029292607836</v>
+        <v>40.84370694067245</v>
       </c>
       <c r="E83">
-        <v>20.753</v>
+        <v>21.166</v>
       </c>
       <c r="F83">
-        <v>33.453</v>
+        <v>33.866</v>
       </c>
       <c r="G83">
         <v>1.12</v>
@@ -8081,28 +8081,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M83">
-        <v>2.1443373</v>
+        <v>2.1708106</v>
       </c>
       <c r="N83">
-        <v>4.939132087755102</v>
+        <v>4.912658787755102</v>
       </c>
       <c r="O83">
-        <v>1.382956984571429</v>
+        <v>1.375544460571429</v>
       </c>
       <c r="P83">
-        <v>3.556175103183673</v>
+        <v>3.537114327183673</v>
       </c>
       <c r="Q83">
-        <v>4.646175103183673</v>
+        <v>4.627114327183673</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1412120445036588</v>
+        <v>0.1461480012808786</v>
       </c>
       <c r="T83">
-        <v>2.203511420407825</v>
+        <v>2.317505803253548</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.30333730041216</v>
+        <v>3.263052699187622</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06415128023055815</v>
+        <v>0.06408915200542112</v>
       </c>
       <c r="C84">
-        <v>8.097706940672452</v>
+        <v>7.708147830659669</v>
       </c>
       <c r="D84">
-        <v>40.84370694067245</v>
+        <v>40.86714783065968</v>
       </c>
       <c r="E84">
-        <v>21.166</v>
+        <v>21.579</v>
       </c>
       <c r="F84">
-        <v>33.866</v>
+        <v>34.279</v>
       </c>
       <c r="G84">
         <v>1.12</v>
@@ -8163,28 +8163,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M84">
-        <v>2.1708106</v>
+        <v>2.1972839</v>
       </c>
       <c r="N84">
-        <v>4.912658787755102</v>
+        <v>4.886185487755101</v>
       </c>
       <c r="O84">
-        <v>1.375544460571429</v>
+        <v>1.368131936571429</v>
       </c>
       <c r="P84">
-        <v>3.537114327183673</v>
+        <v>3.518053551183673</v>
       </c>
       <c r="Q84">
-        <v>4.627114327183673</v>
+        <v>4.608053551183673</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1461480012808786</v>
+        <v>0.1516646588554184</v>
       </c>
       <c r="T84">
-        <v>2.317505803253548</v>
+        <v>2.444911289963474</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.263052699187622</v>
+        <v>3.223738811245602</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06408915200542112</v>
+        <v>0.0640270237802841</v>
       </c>
       <c r="C85">
-        <v>7.708147830659669</v>
+        <v>7.318615642339303</v>
       </c>
       <c r="D85">
-        <v>40.86714783065968</v>
+        <v>40.89061564233931</v>
       </c>
       <c r="E85">
-        <v>21.579</v>
+        <v>21.992</v>
       </c>
       <c r="F85">
-        <v>34.279</v>
+        <v>34.692</v>
       </c>
       <c r="G85">
         <v>1.12</v>
@@ -8245,28 +8245,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M85">
-        <v>2.1972839</v>
+        <v>2.2237572</v>
       </c>
       <c r="N85">
-        <v>4.886185487755101</v>
+        <v>4.859712187755102</v>
       </c>
       <c r="O85">
-        <v>1.368131936571429</v>
+        <v>1.360719412571429</v>
       </c>
       <c r="P85">
-        <v>3.518053551183673</v>
+        <v>3.498992775183673</v>
       </c>
       <c r="Q85">
-        <v>4.608053551183673</v>
+        <v>4.588992775183673</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1516646588554184</v>
+        <v>0.1578708986267757</v>
       </c>
       <c r="T85">
-        <v>2.444911289963474</v>
+        <v>2.588242462512141</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.223738811245602</v>
+        <v>3.185360968254584</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0640270237802841</v>
+        <v>0.06396489555514707</v>
       </c>
       <c r="C86">
-        <v>7.31861564233931</v>
+        <v>6.929110422117041</v>
       </c>
       <c r="D86">
-        <v>40.89061564233931</v>
+        <v>40.91411042211704</v>
       </c>
       <c r="E86">
-        <v>21.99199999999999</v>
+        <v>22.405</v>
       </c>
       <c r="F86">
-        <v>34.69199999999999</v>
+        <v>35.105</v>
       </c>
       <c r="G86">
         <v>1.12</v>
@@ -8327,28 +8327,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M86">
-        <v>2.2237572</v>
+        <v>2.2502305</v>
       </c>
       <c r="N86">
-        <v>4.859712187755102</v>
+        <v>4.833238887755102</v>
       </c>
       <c r="O86">
-        <v>1.360719412571429</v>
+        <v>1.353306888571429</v>
       </c>
       <c r="P86">
-        <v>3.498992775183673</v>
+        <v>3.479931999183673</v>
       </c>
       <c r="Q86">
-        <v>4.588992775183673</v>
+        <v>4.569931999183673</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1578708986267756</v>
+        <v>0.1649046370343138</v>
       </c>
       <c r="T86">
-        <v>2.588242462512139</v>
+        <v>2.750684458067294</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.185360968254584</v>
+        <v>3.147886133333942</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06396489555514707</v>
+        <v>0.06390276733001005</v>
       </c>
       <c r="C87">
-        <v>6.929110422117041</v>
+        <v>6.539632216505318</v>
       </c>
       <c r="D87">
-        <v>40.91411042211704</v>
+        <v>40.93763221650531</v>
       </c>
       <c r="E87">
-        <v>22.405</v>
+        <v>22.81799999999999</v>
       </c>
       <c r="F87">
-        <v>35.105</v>
+        <v>35.51799999999999</v>
       </c>
       <c r="G87">
         <v>1.12</v>
@@ -8409,28 +8409,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M87">
-        <v>2.2502305</v>
+        <v>2.2767038</v>
       </c>
       <c r="N87">
-        <v>4.833238887755102</v>
+        <v>4.806765587755102</v>
       </c>
       <c r="O87">
-        <v>1.353306888571429</v>
+        <v>1.345894364571429</v>
       </c>
       <c r="P87">
-        <v>3.479931999183673</v>
+        <v>3.460871223183673</v>
       </c>
       <c r="Q87">
-        <v>4.569931999183673</v>
+        <v>4.550871223183673</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1649046370343138</v>
+        <v>0.1729431952143575</v>
       </c>
       <c r="T87">
-        <v>2.750684458067294</v>
+        <v>2.936332452987472</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.147886133333942</v>
+        <v>3.111282806202151</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06390276733001005</v>
+        <v>0.06384063910487303</v>
       </c>
       <c r="C88">
-        <v>6.539632216505318</v>
+        <v>6.150181072123551</v>
       </c>
       <c r="D88">
-        <v>40.93763221650531</v>
+        <v>40.96118107212355</v>
       </c>
       <c r="E88">
-        <v>22.81799999999999</v>
+        <v>23.231</v>
       </c>
       <c r="F88">
-        <v>35.51799999999999</v>
+        <v>35.931</v>
       </c>
       <c r="G88">
         <v>1.12</v>
@@ -8491,28 +8491,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M88">
-        <v>2.2767038</v>
+        <v>2.3031771</v>
       </c>
       <c r="N88">
-        <v>4.806765587755102</v>
+        <v>4.780292287755102</v>
       </c>
       <c r="O88">
-        <v>1.345894364571429</v>
+        <v>1.338481840571429</v>
       </c>
       <c r="P88">
-        <v>3.460871223183673</v>
+        <v>3.441810447183673</v>
       </c>
       <c r="Q88">
-        <v>4.550871223183673</v>
+        <v>4.531810447183673</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1729431952143575</v>
+        <v>0.1822184546528695</v>
       </c>
       <c r="T88">
-        <v>2.936332452987472</v>
+        <v>3.150541677895369</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.111282806202151</v>
+        <v>3.075520934866494</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06384063910487303</v>
+        <v>0.063778510879736</v>
       </c>
       <c r="C89">
-        <v>6.150181072123551</v>
+        <v>5.760757035698532</v>
       </c>
       <c r="D89">
-        <v>40.96118107212355</v>
+        <v>40.98475703569854</v>
       </c>
       <c r="E89">
-        <v>23.231</v>
+        <v>23.644</v>
       </c>
       <c r="F89">
-        <v>35.931</v>
+        <v>36.344</v>
       </c>
       <c r="G89">
         <v>1.12</v>
@@ -8573,28 +8573,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M89">
-        <v>2.3031771</v>
+        <v>2.3296504</v>
       </c>
       <c r="N89">
-        <v>4.780292287755102</v>
+        <v>4.753818987755102</v>
       </c>
       <c r="O89">
-        <v>1.338481840571429</v>
+        <v>1.331069316571428</v>
       </c>
       <c r="P89">
-        <v>3.441810447183673</v>
+        <v>3.422749671183673</v>
       </c>
       <c r="Q89">
-        <v>4.531810447183673</v>
+        <v>4.512749671183673</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1822184546528695</v>
+        <v>0.1930395906644667</v>
       </c>
       <c r="T89">
-        <v>3.150541677895369</v>
+        <v>3.400452440287916</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.075520934866494</v>
+        <v>3.04057183333392</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.063778510879736</v>
+        <v>0.06371638265459897</v>
       </c>
       <c r="C90">
-        <v>5.760757035698532</v>
+        <v>5.371360154064682</v>
       </c>
       <c r="D90">
-        <v>40.98475703569854</v>
+        <v>41.00836015406468</v>
       </c>
       <c r="E90">
-        <v>23.644</v>
+        <v>24.057</v>
       </c>
       <c r="F90">
-        <v>36.344</v>
+        <v>36.757</v>
       </c>
       <c r="G90">
         <v>1.12</v>
@@ -8655,28 +8655,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M90">
-        <v>2.3296504</v>
+        <v>2.3561237</v>
       </c>
       <c r="N90">
-        <v>4.753818987755102</v>
+        <v>4.727345687755102</v>
       </c>
       <c r="O90">
-        <v>1.331069316571428</v>
+        <v>1.323656792571429</v>
       </c>
       <c r="P90">
-        <v>3.422749671183673</v>
+        <v>3.403688895183674</v>
       </c>
       <c r="Q90">
-        <v>4.512749671183673</v>
+        <v>4.493688895183674</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1930395906644667</v>
+        <v>0.2058282059508999</v>
       </c>
       <c r="T90">
-        <v>3.400452440287916</v>
+        <v>3.695801523115471</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.04057183333392</v>
+        <v>3.006408104869495</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06371638265459897</v>
+        <v>0.06870865442946196</v>
       </c>
       <c r="C91">
-        <v>5.371360154064682</v>
+        <v>3.144589333424257</v>
       </c>
       <c r="D91">
-        <v>41.00836015406468</v>
+        <v>39.19458933342426</v>
       </c>
       <c r="E91">
-        <v>24.057</v>
+        <v>24.47</v>
       </c>
       <c r="F91">
-        <v>36.757</v>
+        <v>37.17</v>
       </c>
       <c r="G91">
         <v>1.12</v>
@@ -8737,45 +8737,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M91">
-        <v>2.3561237</v>
+        <v>2.672523</v>
       </c>
       <c r="N91">
-        <v>4.727345687755102</v>
+        <v>4.410946387755102</v>
       </c>
       <c r="O91">
-        <v>1.323656792571429</v>
+        <v>1.235064988571429</v>
       </c>
       <c r="P91">
-        <v>3.403688895183674</v>
+        <v>3.175881399183673</v>
       </c>
       <c r="Q91">
-        <v>4.493688895183674</v>
+        <v>4.265881399183673</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2058282059508999</v>
+        <v>0.2211745442946197</v>
       </c>
       <c r="T91">
-        <v>3.695801523115471</v>
+        <v>4.050220422508538</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.28</v>
       </c>
       <c r="W91">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.006408104869495</v>
+        <v>2.650480234503164</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06870865442946196</v>
+        <v>0.06870268620432494</v>
       </c>
       <c r="C92">
-        <v>3.144589333424257</v>
+        <v>2.733661888441908</v>
       </c>
       <c r="D92">
-        <v>39.19458933342426</v>
+        <v>39.19666188844191</v>
       </c>
       <c r="E92">
-        <v>24.47</v>
+        <v>24.883</v>
       </c>
       <c r="F92">
-        <v>37.17</v>
+        <v>37.583</v>
       </c>
       <c r="G92">
         <v>1.12</v>
@@ -8819,28 +8819,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M92">
-        <v>2.672523</v>
+        <v>2.7022177</v>
       </c>
       <c r="N92">
-        <v>4.410946387755102</v>
+        <v>4.381251687755102</v>
       </c>
       <c r="O92">
-        <v>1.235064988571429</v>
+        <v>1.226750472571428</v>
       </c>
       <c r="P92">
-        <v>3.175881399183673</v>
+        <v>3.154501215183673</v>
       </c>
       <c r="Q92">
-        <v>4.265881399183673</v>
+        <v>4.244501215183673</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2211745442946197</v>
+        <v>0.2399311800480549</v>
       </c>
       <c r="T92">
-        <v>4.050220422508538</v>
+        <v>4.483399077322285</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.650480234503164</v>
+        <v>2.621354078080053</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06870268620432494</v>
+        <v>0.06869671797918792</v>
       </c>
       <c r="C93">
-        <v>2.733661888441908</v>
+        <v>2.322734662658767</v>
       </c>
       <c r="D93">
-        <v>39.19666188844191</v>
+        <v>39.19873466265877</v>
       </c>
       <c r="E93">
-        <v>24.883</v>
+        <v>25.296</v>
       </c>
       <c r="F93">
-        <v>37.583</v>
+        <v>37.996</v>
       </c>
       <c r="G93">
         <v>1.12</v>
@@ -8901,28 +8901,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M93">
-        <v>2.7022177</v>
+        <v>2.731912400000001</v>
       </c>
       <c r="N93">
-        <v>4.381251687755102</v>
+        <v>4.351556987755101</v>
       </c>
       <c r="O93">
-        <v>1.226750472571428</v>
+        <v>1.218435956571428</v>
       </c>
       <c r="P93">
-        <v>3.154501215183673</v>
+        <v>3.133121031183673</v>
       </c>
       <c r="Q93">
-        <v>4.244501215183673</v>
+        <v>4.223121031183672</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2399311800480549</v>
+        <v>0.2633769747398491</v>
       </c>
       <c r="T93">
-        <v>4.483399077322285</v>
+        <v>5.024872395839471</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.621354078080053</v>
+        <v>2.592861098970487</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06869671797918792</v>
+        <v>0.0686907497540509</v>
       </c>
       <c r="C94">
-        <v>2.322734662658767</v>
+        <v>1.911807656109602</v>
       </c>
       <c r="D94">
-        <v>39.19873466265877</v>
+        <v>39.2008076561096</v>
       </c>
       <c r="E94">
-        <v>25.296</v>
+        <v>25.709</v>
       </c>
       <c r="F94">
-        <v>37.996</v>
+        <v>38.409</v>
       </c>
       <c r="G94">
         <v>1.12</v>
@@ -8983,28 +8983,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M94">
-        <v>2.731912400000001</v>
+        <v>2.7616071</v>
       </c>
       <c r="N94">
-        <v>4.351556987755101</v>
+        <v>4.321862287755102</v>
       </c>
       <c r="O94">
-        <v>1.218435956571428</v>
+        <v>1.210121440571429</v>
       </c>
       <c r="P94">
-        <v>3.133121031183673</v>
+        <v>3.111740847183673</v>
       </c>
       <c r="Q94">
-        <v>4.223121031183672</v>
+        <v>4.201740847183673</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2633769747398491</v>
+        <v>0.2935215679150129</v>
       </c>
       <c r="T94">
-        <v>5.024872395839471</v>
+        <v>5.721052376790137</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.592861098970487</v>
+        <v>2.564980872099837</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0686907497540509</v>
+        <v>0.06868478152891387</v>
       </c>
       <c r="C95">
-        <v>1.911807656109602</v>
+        <v>1.500880868829213</v>
       </c>
       <c r="D95">
-        <v>39.2008076561096</v>
+        <v>39.20288086882922</v>
       </c>
       <c r="E95">
-        <v>25.709</v>
+        <v>26.122</v>
       </c>
       <c r="F95">
-        <v>38.409</v>
+        <v>38.822</v>
       </c>
       <c r="G95">
         <v>1.12</v>
@@ -9065,28 +9065,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M95">
-        <v>2.7616071</v>
+        <v>2.7913018</v>
       </c>
       <c r="N95">
-        <v>4.321862287755102</v>
+        <v>4.292167587755102</v>
       </c>
       <c r="O95">
-        <v>1.210121440571429</v>
+        <v>1.201806924571428</v>
       </c>
       <c r="P95">
-        <v>3.111740847183673</v>
+        <v>3.090360663183673</v>
       </c>
       <c r="Q95">
-        <v>4.201740847183673</v>
+        <v>4.180360663183673</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.2935215679150129</v>
+        <v>0.3337143588152314</v>
       </c>
       <c r="T95">
-        <v>5.721052376790137</v>
+        <v>6.649292351391026</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.564980872099837</v>
+        <v>2.537693841545583</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06868478152891387</v>
+        <v>0.06867881330377684</v>
       </c>
       <c r="C96">
-        <v>1.500880868829213</v>
+        <v>1.089954300852384</v>
       </c>
       <c r="D96">
-        <v>39.20288086882922</v>
+        <v>39.20495430085239</v>
       </c>
       <c r="E96">
-        <v>26.122</v>
+        <v>26.535</v>
       </c>
       <c r="F96">
-        <v>38.822</v>
+        <v>39.235</v>
       </c>
       <c r="G96">
         <v>1.12</v>
@@ -9147,28 +9147,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M96">
-        <v>2.7913018</v>
+        <v>2.8209965</v>
       </c>
       <c r="N96">
-        <v>4.292167587755102</v>
+        <v>4.262472887755102</v>
       </c>
       <c r="O96">
-        <v>1.201806924571428</v>
+        <v>1.193492408571429</v>
       </c>
       <c r="P96">
-        <v>3.090360663183673</v>
+        <v>3.068980479183673</v>
       </c>
       <c r="Q96">
-        <v>4.180360663183673</v>
+        <v>4.158980479183674</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3337143588152314</v>
+        <v>0.3899842660755373</v>
       </c>
       <c r="T96">
-        <v>6.649292351391026</v>
+        <v>7.948828315832272</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.537693841545583</v>
+        <v>2.510981274792472</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06867881330377684</v>
+        <v>0.07136852507863982</v>
       </c>
       <c r="C97">
-        <v>1.089954300852384</v>
+        <v>-0.2357770014784464</v>
       </c>
       <c r="D97">
-        <v>39.20495430085239</v>
+        <v>38.29222299852156</v>
       </c>
       <c r="E97">
-        <v>26.535</v>
+        <v>26.948</v>
       </c>
       <c r="F97">
-        <v>39.235</v>
+        <v>39.648</v>
       </c>
       <c r="G97">
         <v>1.12</v>
@@ -9229,45 +9229,45 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M97">
-        <v>2.8209965</v>
+        <v>3.005318400000001</v>
       </c>
       <c r="N97">
-        <v>4.262472887755102</v>
+        <v>4.078150987755102</v>
       </c>
       <c r="O97">
-        <v>1.193492408571429</v>
+        <v>1.141882276571428</v>
       </c>
       <c r="P97">
-        <v>3.068980479183673</v>
+        <v>2.936268711183673</v>
       </c>
       <c r="Q97">
-        <v>4.158980479183674</v>
+        <v>4.026268711183673</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.3899842660755373</v>
+        <v>0.4743891269659963</v>
       </c>
       <c r="T97">
-        <v>7.948828315832272</v>
+        <v>9.898132262494142</v>
       </c>
       <c r="U97">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V97">
         <v>0.28</v>
       </c>
       <c r="W97">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.510981274792472</v>
+        <v>2.356978011965421</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07136852507863982</v>
+        <v>0.07139063685350279</v>
       </c>
       <c r="C98">
-        <v>-0.2357770014784393</v>
+        <v>-0.656104357951321</v>
       </c>
       <c r="D98">
-        <v>38.29222299852156</v>
+        <v>38.28489564204867</v>
       </c>
       <c r="E98">
-        <v>26.948</v>
+        <v>27.36099999999999</v>
       </c>
       <c r="F98">
-        <v>39.648</v>
+        <v>40.06099999999999</v>
       </c>
       <c r="G98">
         <v>1.12</v>
@@ -9311,28 +9311,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M98">
-        <v>3.0053184</v>
+        <v>3.0366238</v>
       </c>
       <c r="N98">
-        <v>4.078150987755102</v>
+        <v>4.046845587755103</v>
       </c>
       <c r="O98">
-        <v>1.141882276571428</v>
+        <v>1.133116764571429</v>
       </c>
       <c r="P98">
-        <v>2.936268711183673</v>
+        <v>2.913728823183674</v>
       </c>
       <c r="Q98">
-        <v>4.026268711183673</v>
+        <v>4.003728823183674</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.4743891269659951</v>
+        <v>0.6150638951167594</v>
       </c>
       <c r="T98">
-        <v>9.898132262494116</v>
+        <v>13.14697217359722</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.356978011965421</v>
+        <v>2.332679269574026</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07139063685350279</v>
+        <v>0.07141274862836577</v>
       </c>
       <c r="C99">
-        <v>-0.656104357951321</v>
+        <v>-1.076428910727962</v>
       </c>
       <c r="D99">
-        <v>38.28489564204867</v>
+        <v>38.27757108927204</v>
       </c>
       <c r="E99">
-        <v>27.36099999999999</v>
+        <v>27.774</v>
       </c>
       <c r="F99">
-        <v>40.06099999999999</v>
+        <v>40.474</v>
       </c>
       <c r="G99">
         <v>1.12</v>
@@ -9393,28 +9393,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M99">
-        <v>3.0366238</v>
+        <v>3.0679292</v>
       </c>
       <c r="N99">
-        <v>4.046845587755103</v>
+        <v>4.015540187755102</v>
       </c>
       <c r="O99">
-        <v>1.133116764571429</v>
+        <v>1.124351252571429</v>
       </c>
       <c r="P99">
-        <v>2.913728823183674</v>
+        <v>2.891188935183673</v>
       </c>
       <c r="Q99">
-        <v>4.003728823183674</v>
+        <v>3.981188935183673</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6150638951167594</v>
+        <v>0.8964134314182878</v>
       </c>
       <c r="T99">
-        <v>13.14697217359722</v>
+        <v>19.64465199580342</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.332679269574026</v>
+        <v>2.308876419884495</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07141274862836577</v>
+        <v>0.07143486040322874</v>
       </c>
       <c r="C100">
-        <v>-1.076428910727962</v>
+        <v>-1.496750661417217</v>
       </c>
       <c r="D100">
-        <v>38.27757108927204</v>
+        <v>38.27024933858278</v>
       </c>
       <c r="E100">
-        <v>27.774</v>
+        <v>28.18699999999999</v>
       </c>
       <c r="F100">
-        <v>40.474</v>
+        <v>40.88699999999999</v>
       </c>
       <c r="G100">
         <v>1.12</v>
@@ -9475,28 +9475,28 @@
         <v>7.083469387755102</v>
       </c>
       <c r="M100">
-        <v>3.0679292</v>
+        <v>3.0992346</v>
       </c>
       <c r="N100">
-        <v>4.015540187755102</v>
+        <v>3.984234787755102</v>
       </c>
       <c r="O100">
-        <v>1.124351252571429</v>
+        <v>1.115585740571429</v>
       </c>
       <c r="P100">
-        <v>2.891188935183673</v>
+        <v>2.868649047183673</v>
       </c>
       <c r="Q100">
-        <v>3.981188935183673</v>
+        <v>3.958649047183673</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.8964134314182878</v>
+        <v>1.740462040322873</v>
       </c>
       <c r="T100">
-        <v>19.64465199580342</v>
+        <v>39.13769146242203</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.308876419884495</v>
+        <v>2.285554435845257</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07143486040322874</v>
-      </c>
-      <c r="C101">
-        <v>-1.496750661417217</v>
-      </c>
-      <c r="D101">
-        <v>38.27024933858278</v>
-      </c>
-      <c r="E101">
-        <v>28.18699999999999</v>
-      </c>
-      <c r="F101">
-        <v>40.88699999999999</v>
-      </c>
-      <c r="G101">
-        <v>1.12</v>
-      </c>
-      <c r="H101">
-        <v>28.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.173469387755102</v>
-      </c>
-      <c r="K101">
-        <v>1.09</v>
-      </c>
-      <c r="L101">
-        <v>7.083469387755102</v>
-      </c>
-      <c r="M101">
-        <v>3.0992346</v>
-      </c>
-      <c r="N101">
-        <v>3.984234787755102</v>
-      </c>
-      <c r="O101">
-        <v>1.115585740571429</v>
-      </c>
-      <c r="P101">
-        <v>2.868649047183673</v>
-      </c>
-      <c r="Q101">
-        <v>3.958649047183673</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.740462040322873</v>
-      </c>
-      <c r="T101">
-        <v>39.13769146242203</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.28</v>
-      </c>
-      <c r="W101">
-        <v>0.054576</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.285554435845257</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
